--- a/planering/biologi-planering.xlsx
+++ b/planering/biologi-planering.xlsx
@@ -496,7 +496,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Syftesdelar härleds: F1→S2, F3→S7, SU3→S6, SU4→S4. S1, S3, S5, S8 är satta för hand.</t>
+          <t>Syfte: den del av ämnets syfte (i sak) som momentet bygger på. Delar som följer av förmåga eller innehåll är härledda automatiskt.</t>
         </is>
       </c>
     </row>
@@ -659,17 +659,17 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>S1 Nyfikenhet och frågor; S7 Systematiska undersökningar</t>
+          <t>Nyfikenhet och intresse; ställa frågor om natur och människa utifrån egna upplevelser och aktuella händelser; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>SU1 Undersökningar</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>S7 Systematiska undersökningar</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>SU1 Undersökningar</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -785,17 +785,17 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>S7 Systematiska undersökningar</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>SU1 Undersökningar</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>S7 Systematiska undersökningar; S8 Material, utrustning, digitalt</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder; Färdigheter i att hantera material, utrustning och digitala verktyg</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>SU1 Undersökningar</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -907,13 +907,13 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>S1 Nyfikenhet och frågor; S2 Begrepp och samband</t>
+          <t>Nyfikenhet och intresse; ställa frågor om natur och människa utifrån egna upplevelser och aktuella händelser; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -962,17 +962,17 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>S1 Nyfikenhet och frågor; S7 Systematiska undersökningar</t>
+          <t>Nyfikenhet och intresse; ställa frågor om natur och människa utifrån egna upplevelser och aktuella händelser; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>SU1 Undersökningar</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -1021,17 +1021,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>S8 Material, utrustning, digitalt; S7 Systematiska undersökningar</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>SU1 Undersökningar</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1084,17 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>S3 Evolution och världsbild; S6 Källor och kritiskt tänkande</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>SU3 Informationsgranskning</t>
+          <t>Informationsgranskning</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>S7 Systematiska undersökningar; S2 Begrepp och samband</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>SU2 Modeller och historia</t>
+          <t>Modeller och historia</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -1210,17 +1210,17 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>S6 Källor och kritiskt tänkande</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>SU3 Informationsgranskning</t>
+          <t>Informationsgranskning</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>S6 Källor och kritiskt tänkande</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>SU3 Informationsgranskning</t>
+          <t>Informationsgranskning</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -1332,17 +1332,17 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>SU2 Modeller och historia</t>
+          <t>Modeller och historia</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>S3 Evolution och världsbild</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>SU2 Modeller och historia</t>
+          <t>Modeller och historia</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr"/>
@@ -1446,17 +1446,17 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>S6 Källor och kritiskt tänkande</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>SU3 Informationsgranskning</t>
+          <t>Informationsgranskning</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -1505,17 +1505,17 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>S6 Källor och kritiskt tänkande</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>SU3 Informationsgranskning; SU1 Undersökningar</t>
+          <t>Informationsgranskning; Undersökningar</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -1564,17 +1564,17 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>S4 Argument och kommunikation</t>
+          <t>Formulera egna och granska andras argument; kommunicera</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>SU4 Argumentation</t>
+          <t>Argumentation</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -1627,17 +1627,17 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem; SU2 Modeller och historia</t>
+          <t>Celler och organsystem; Modeller och historia</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -1690,17 +1690,17 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -1753,17 +1753,17 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -1816,17 +1816,17 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>S8 Material, utrustning, digitalt; S7 Systematiska undersökningar</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem; SU1 Undersökningar</t>
+          <t>Celler och organsystem; Undersökningar</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -1875,17 +1875,17 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband; S7 Systematiska undersökningar</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller; F3 Undersöka</t>
+          <t>Begrepp/modeller; Undersöka</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>S3 Evolution och världsbild</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr"/>
@@ -1993,17 +1993,17 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -2056,17 +2056,17 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi; KH1 Celler och organsystem</t>
+          <t>Fotosyntes, kretslopp, energi; Celler och organsystem</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -2119,17 +2119,17 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -2182,17 +2182,17 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>S8 Material, utrustning, digitalt; S7 Systematiska undersökningar</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi; SU1 Undersökningar</t>
+          <t>Fotosyntes, kretslopp, energi; Undersökningar</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -2241,17 +2241,17 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi; KH1 Celler och organsystem</t>
+          <t>Fotosyntes, kretslopp, energi; Celler och organsystem</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -2300,17 +2300,17 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>S7 Systematiska undersökningar</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi; SU1 Undersökningar</t>
+          <t>Fotosyntes, kretslopp, energi; Undersökningar</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -2359,17 +2359,17 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -2418,17 +2418,17 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -2481,17 +2481,17 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -2544,17 +2544,17 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald; NM6 Påverkan och hållbarhet</t>
+          <t>Evolution och mångfald; Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -2729,17 +2729,17 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>NM6 Påverkan och hållbarhet</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -2792,17 +2792,17 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>NM6 Påverkan och hållbarhet</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -2855,17 +2855,17 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>S8 Material, utrustning, digitalt; S7 Systematiska undersökningar</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>NM6 Påverkan och hållbarhet; SU1 Undersökningar</t>
+          <t>Påverkan och hållbarhet; Undersökningar</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -2914,17 +2914,17 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>S7 Systematiska undersökningar</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>NM6 Påverkan och hållbarhet; SU1 Undersökningar</t>
+          <t>Påverkan och hållbarhet; Undersökningar</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -2973,17 +2973,17 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald; NM4 Ekosystem och populationer</t>
+          <t>Evolution och mångfald; Ekosystem och populationer</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -3036,17 +3036,17 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -3099,17 +3099,17 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>S7 Systematiska undersökningar</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>SU1 Undersökningar</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -3162,17 +3162,17 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>S3 Evolution och världsbild; S2 Begrepp och samband</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -3225,17 +3225,17 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>S8 Material, utrustning, digitalt; S7 Systematiska undersökningar</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald; SU1 Undersökningar</t>
+          <t>Evolution och mångfald; Undersökningar</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -3284,17 +3284,17 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -3343,17 +3343,17 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -3402,17 +3402,17 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -3461,17 +3461,17 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -3520,17 +3520,17 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald; NM4 Ekosystem och populationer</t>
+          <t>Evolution och mångfald; Ekosystem och populationer</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -3579,17 +3579,17 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -3638,17 +3638,17 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -3701,17 +3701,17 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>NM4 Ekosystem och populationer</t>
+          <t>Ekosystem och populationer</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -3764,17 +3764,17 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>NM4 Ekosystem och populationer; NM5 Fotosyntes, kretslopp, energi</t>
+          <t>Ekosystem och populationer; Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -3827,17 +3827,17 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -3890,17 +3890,17 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>S7 Systematiska undersökningar</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi; SU1 Undersökningar</t>
+          <t>Fotosyntes, kretslopp, energi; Undersökningar</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -3949,17 +3949,17 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>NM4 Ekosystem och populationer</t>
+          <t>Ekosystem och populationer</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -4008,17 +4008,17 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>NM4 Ekosystem och populationer</t>
+          <t>Ekosystem och populationer</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -4067,17 +4067,17 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>NM4 Ekosystem och populationer; NM5 Fotosyntes, kretslopp, energi</t>
+          <t>Ekosystem och populationer; Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -4127,12 +4127,12 @@
       <c r="K59" s="4" t="inlineStr"/>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>NM4 Ekosystem och populationer</t>
+          <t>Ekosystem och populationer</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -4185,17 +4185,17 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -4311,17 +4311,17 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -4374,17 +4374,17 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>S8 Material, utrustning, digitalt; S7 Systematiska undersökningar</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi; SU1 Undersökningar</t>
+          <t>Fotosyntes, kretslopp, energi; Undersökningar</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -4433,17 +4433,17 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -4496,17 +4496,17 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>NM4 Ekosystem och populationer; SU1 Undersökningar</t>
+          <t>Ekosystem och populationer; Undersökningar</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -4559,17 +4559,17 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>NM4 Ekosystem och populationer</t>
+          <t>Ekosystem och populationer</t>
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -4622,17 +4622,17 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>S3 Evolution och världsbild; S2 Begrepp och samband</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>NM4 Ekosystem och populationer; NM1 Evolution och mångfald</t>
+          <t>Ekosystem och populationer; Evolution och mångfald</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -4685,17 +4685,17 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>S7 Systematiska undersökningar</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>NM4 Ekosystem och populationer; SU1 Undersökningar</t>
+          <t>Ekosystem och populationer; Undersökningar</t>
         </is>
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -4744,17 +4744,17 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>NM4 Ekosystem och populationer</t>
+          <t>Ekosystem och populationer</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -4807,17 +4807,17 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>NM6 Påverkan och hållbarhet</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -4870,17 +4870,17 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi; NM6 Påverkan och hållbarhet</t>
+          <t>Fotosyntes, kretslopp, energi; Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -4933,17 +4933,17 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>NM6 Påverkan och hållbarhet</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -4996,17 +4996,17 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>S8 Material, utrustning, digitalt; S7 Systematiska undersökningar</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi; NM6 Påverkan och hållbarhet; SU1 Undersökningar</t>
+          <t>Fotosyntes, kretslopp, energi; Påverkan och hållbarhet; Undersökningar</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -5055,17 +5055,17 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>NM6 Påverkan och hållbarhet</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -5114,17 +5114,17 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>NM6 Påverkan och hållbarhet; NM5 Fotosyntes, kretslopp, energi</t>
+          <t>Påverkan och hållbarhet; Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -5173,17 +5173,17 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>NM6 Påverkan och hållbarhet</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -5233,12 +5233,12 @@
       <c r="K77" s="4" t="inlineStr"/>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>NM5 Fotosyntes, kretslopp, energi; NM6 Påverkan och hållbarhet</t>
+          <t>Fotosyntes, kretslopp, energi; Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -5291,17 +5291,17 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>S5 Etiska val; S2 Begrepp och samband</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>NM6 Påverkan och hållbarhet</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -5354,17 +5354,17 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>NM6 Påverkan och hållbarhet</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>S5 Etiska val</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>NM6 Påverkan och hållbarhet</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -5480,17 +5480,17 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>S4 Argument och kommunikation; S5 Etiska val</t>
+          <t>Formulera egna och granska andras argument; kommunicera; Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>SU4 Argumentation</t>
+          <t>Argumentation</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -5539,17 +5539,17 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>S4 Argument och kommunikation; S5 Etiska val</t>
+          <t>Formulera egna och granska andras argument; kommunicera; Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>SU4 Argumentation</t>
+          <t>Argumentation</t>
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -5602,17 +5602,17 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem; KH3 Hälsa</t>
+          <t>Celler och organsystem; Hälsa</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -5665,17 +5665,17 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -5728,17 +5728,17 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -5791,17 +5791,17 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>S8 Material, utrustning, digitalt; S7 Systematiska undersökningar</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem; SU1 Undersökningar</t>
+          <t>Celler och organsystem; Undersökningar</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -5850,17 +5850,17 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem; KH3 Hälsa</t>
+          <t>Celler och organsystem; Hälsa</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -5909,17 +5909,17 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="M88" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -5968,17 +5968,17 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -6027,17 +6027,17 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem; KH2 Infektioner</t>
+          <t>Celler och organsystem; Infektioner</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -6087,12 +6087,12 @@
       <c r="K91" s="4" t="inlineStr"/>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa; NM6 Påverkan och hållbarhet</t>
+          <t>Hälsa; Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>S6 Källor och kritiskt tänkande; S4 Argument och kommunikation</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan; Formulera egna och granska andras argument; kommunicera</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa; SU3 Informationsgranskning; SU4 Argumentation</t>
+          <t>Hälsa; Informationsgranskning; Argumentation</t>
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -6204,17 +6204,17 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -6267,17 +6267,17 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -6330,17 +6330,17 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -6393,17 +6393,17 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>S8 Material, utrustning, digitalt; S7 Systematiska undersökningar</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem; KH3 Hälsa; SU1 Undersökningar</t>
+          <t>Celler och organsystem; Hälsa; Undersökningar</t>
         </is>
       </c>
       <c r="M96" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -6452,17 +6452,17 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem; NM5 Fotosyntes, kretslopp, energi</t>
+          <t>Celler och organsystem; Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -6511,17 +6511,17 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="M98" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -6570,17 +6570,17 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -6629,17 +6629,17 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem; KH3 Hälsa</t>
+          <t>Celler och organsystem; Hälsa</t>
         </is>
       </c>
       <c r="M100" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -6692,17 +6692,17 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>KH2 Infektioner</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -6755,17 +6755,17 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>KH2 Infektioner</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="M102" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -6818,17 +6818,17 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>KH2 Infektioner; KH3 Hälsa</t>
+          <t>Infektioner; Hälsa</t>
         </is>
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -6881,17 +6881,17 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>S7 Systematiska undersökningar</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>KH2 Infektioner; SU1 Undersökningar</t>
+          <t>Infektioner; Undersökningar</t>
         </is>
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -6940,17 +6940,17 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>KH2 Infektioner</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -7003,17 +7003,17 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>KH2 Infektioner</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -7066,17 +7066,17 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>KH2 Infektioner</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -7129,17 +7129,17 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>S3 Evolution och världsbild; S2 Begrepp och samband</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>KH2 Infektioner; NM1 Evolution och mångfald</t>
+          <t>Infektioner; Evolution och mångfald</t>
         </is>
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -7192,17 +7192,17 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>S6 Källor och kritiskt tänkande</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>KH2 Infektioner; SU3 Informationsgranskning</t>
+          <t>Infektioner; Informationsgranskning</t>
         </is>
       </c>
       <c r="M109" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -7251,17 +7251,17 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>KH2 Infektioner</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="M110" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -7310,17 +7310,17 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>KH2 Infektioner</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -7369,17 +7369,17 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>KH2 Infektioner</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -7428,17 +7428,17 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>S6 Källor och kritiskt tänkande; S4 Argument och kommunikation</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan; Formulera egna och granska andras argument; kommunicera</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>KH2 Infektioner; SU3 Informationsgranskning; SU4 Argumentation</t>
+          <t>Infektioner; Informationsgranskning; Argumentation</t>
         </is>
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -7491,17 +7491,17 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>NM2 Arv och miljö</t>
+          <t>Arv och miljö</t>
         </is>
       </c>
       <c r="M114" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -7554,17 +7554,17 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>NM2 Arv och miljö</t>
+          <t>Arv och miljö</t>
         </is>
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -7617,17 +7617,17 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>NM2 Arv och miljö</t>
+          <t>Arv och miljö</t>
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -7680,17 +7680,17 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>S8 Material, utrustning, digitalt; S7 Systematiska undersökningar</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>NM2 Arv och miljö; SU1 Undersökningar</t>
+          <t>Arv och miljö; Undersökningar</t>
         </is>
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -7739,17 +7739,17 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>NM2 Arv och miljö</t>
+          <t>Arv och miljö</t>
         </is>
       </c>
       <c r="M118" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -7798,17 +7798,17 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>NM2 Arv och miljö</t>
+          <t>Arv och miljö</t>
         </is>
       </c>
       <c r="M119" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -7857,17 +7857,17 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>NM2 Arv och miljö; KH1 Celler och organsystem</t>
+          <t>Arv och miljö; Celler och organsystem</t>
         </is>
       </c>
       <c r="M120" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -7916,17 +7916,17 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>NM2 Arv och miljö</t>
+          <t>Arv och miljö</t>
         </is>
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -7975,17 +7975,17 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>NM2 Arv och miljö; KH3 Hälsa</t>
+          <t>Arv och miljö; Hälsa</t>
         </is>
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -8038,17 +8038,17 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>NM2 Arv och miljö</t>
+          <t>Arv och miljö</t>
         </is>
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -8101,17 +8101,17 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>NM3 Genteknik</t>
+          <t>Genteknik</t>
         </is>
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -8164,17 +8164,17 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>S5 Etiska val; S4 Argument och kommunikation</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa; Formulera egna och granska andras argument; kommunicera</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>NM3 Genteknik; SU4 Argumentation</t>
+          <t>Genteknik; Argumentation</t>
         </is>
       </c>
       <c r="M125" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -8227,17 +8227,17 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>S4 Argument och kommunikation; S5 Etiska val</t>
+          <t>Formulera egna och granska andras argument; kommunicera; Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>NM3 Genteknik; SU4 Argumentation</t>
+          <t>Genteknik; Argumentation</t>
         </is>
       </c>
       <c r="M126" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -8286,17 +8286,17 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>S3 Evolution och världsbild; S2 Begrepp och samband</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>NM2 Arv och miljö; NM1 Evolution och mångfald</t>
+          <t>Arv och miljö; Evolution och mångfald</t>
         </is>
       </c>
       <c r="M127" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -8345,17 +8345,17 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>NM3 Genteknik</t>
+          <t>Genteknik</t>
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -8404,17 +8404,17 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>NM3 Genteknik</t>
+          <t>Genteknik</t>
         </is>
       </c>
       <c r="M129" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -8463,17 +8463,17 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>NM3 Genteknik</t>
+          <t>Genteknik</t>
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -8522,17 +8522,17 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>NM3 Genteknik</t>
+          <t>Genteknik</t>
         </is>
       </c>
       <c r="M131" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -8581,17 +8581,17 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>S5 Etiska val</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>NM3 Genteknik</t>
+          <t>Genteknik</t>
         </is>
       </c>
       <c r="M132" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -8644,17 +8644,17 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="M133" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -8707,17 +8707,17 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="M134" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -8770,17 +8770,17 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald; SU2 Modeller och historia</t>
+          <t>Evolution och mångfald; Modeller och historia</t>
         </is>
       </c>
       <c r="M135" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -8833,17 +8833,17 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>S8 Material, utrustning, digitalt; S7 Systematiska undersökningar</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald; SU2 Modeller och historia</t>
+          <t>Evolution och mångfald; Modeller och historia</t>
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -8892,17 +8892,17 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>S3 Evolution och världsbild; S2 Begrepp och samband</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald; SU2 Modeller och historia</t>
+          <t>Evolution och mångfald; Modeller och historia</t>
         </is>
       </c>
       <c r="M137" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -8951,17 +8951,17 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald; NM2 Arv och miljö</t>
+          <t>Evolution och mångfald; Arv och miljö</t>
         </is>
       </c>
       <c r="M138" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -9014,17 +9014,17 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald; NM2 Arv och miljö</t>
+          <t>Evolution och mångfald; Arv och miljö</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -9077,17 +9077,17 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="M140" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -9140,13 +9140,13 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>S3 Evolution och världsbild; S6 Källor och kritiskt tänkande</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr"/>
       <c r="M141" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -9199,17 +9199,17 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>S7 Systematiska undersökningar</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald; SU1 Undersökningar; SU2 Modeller och historia</t>
+          <t>Evolution och mångfald; Undersökningar; Modeller och historia</t>
         </is>
       </c>
       <c r="M142" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -9258,17 +9258,17 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald; NM2 Arv och miljö</t>
+          <t>Evolution och mångfald; Arv och miljö</t>
         </is>
       </c>
       <c r="M143" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -9317,17 +9317,17 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="M144" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -9376,17 +9376,17 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>S3 Evolution och världsbild; S2 Begrepp och samband</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald; SU2 Modeller och historia</t>
+          <t>Evolution och mångfald; Modeller och historia</t>
         </is>
       </c>
       <c r="M145" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -9439,17 +9439,17 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa; KH1 Celler och organsystem</t>
+          <t>Hälsa; Celler och organsystem</t>
         </is>
       </c>
       <c r="M146" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -9502,17 +9502,17 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="M147" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -9565,17 +9565,17 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="M148" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -9628,17 +9628,17 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>S8 Material, utrustning, digitalt; S7 Systematiska undersökningar; S6 Källor och kritiskt tänkande</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder; Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa; SU1 Undersökningar; SU3 Informationsgranskning</t>
+          <t>Hälsa; Undersökningar; Informationsgranskning</t>
         </is>
       </c>
       <c r="M149" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -9687,17 +9687,17 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="M150" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -9746,17 +9746,17 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -9806,12 +9806,12 @@
       <c r="K152" s="4" t="inlineStr"/>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -9860,17 +9860,17 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -9919,17 +9919,17 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -9982,17 +9982,17 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="M155" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -10045,17 +10045,17 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa; KH1 Celler och organsystem</t>
+          <t>Hälsa; Celler och organsystem</t>
         </is>
       </c>
       <c r="M156" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -10108,17 +10108,17 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>S5 Etiska val; S4 Argument och kommunikation</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa; Formulera egna och granska andras argument; kommunicera</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa; SU4 Argumentation</t>
+          <t>Hälsa; Argumentation</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -10171,17 +10171,17 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>S8 Material, utrustning, digitalt; S7 Systematiska undersökningar; S6 Källor och kritiskt tänkande</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder; Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa; SU1 Undersökningar; SU3 Informationsgranskning</t>
+          <t>Hälsa; Undersökningar; Informationsgranskning</t>
         </is>
       </c>
       <c r="M158" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -10230,17 +10230,17 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
-          <t>KH3 Hälsa</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="M159" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -10293,17 +10293,17 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>KH4 Reproduktion och relationer; KH1 Celler och organsystem</t>
+          <t>Reproduktion och relationer; Celler och organsystem</t>
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -10356,17 +10356,17 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
-          <t>KH4 Reproduktion och relationer</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="M161" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -10419,17 +10419,17 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>KH4 Reproduktion och relationer; KH2 Infektioner</t>
+          <t>Reproduktion och relationer; Infektioner</t>
         </is>
       </c>
       <c r="M162" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -10482,17 +10482,17 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>S6 Källor och kritiskt tänkande</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
-          <t>KH4 Reproduktion och relationer; SU3 Informationsgranskning</t>
+          <t>Reproduktion och relationer; Informationsgranskning</t>
         </is>
       </c>
       <c r="M163" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -10541,17 +10541,17 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>KH4 Reproduktion och relationer</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="M164" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -10600,17 +10600,17 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
-          <t>KH4 Reproduktion och relationer</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="M165" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -10659,17 +10659,17 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>KH4 Reproduktion och relationer</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="M166" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -10718,17 +10718,17 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
-          <t>KH4 Reproduktion och relationer; KH2 Infektioner</t>
+          <t>Reproduktion och relationer; Infektioner</t>
         </is>
       </c>
       <c r="M167" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -10777,17 +10777,17 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>KH4 Reproduktion och relationer</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="M168" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -10840,17 +10840,17 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
-          <t>KH4 Reproduktion och relationer</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="M169" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -10903,17 +10903,17 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>S5 Etiska val</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>KH4 Reproduktion och relationer</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="M170" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -10966,17 +10966,17 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>S5 Etiska val</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
-          <t>KH4 Reproduktion och relationer</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="M171" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -11029,17 +11029,17 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>S5 Etiska val; S4 Argument och kommunikation</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa; Formulera egna och granska andras argument; kommunicera</t>
         </is>
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>KH4 Reproduktion och relationer; SU4 Argumentation</t>
+          <t>Reproduktion och relationer; Argumentation</t>
         </is>
       </c>
       <c r="M172" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -11088,17 +11088,17 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>S6 Källor och kritiskt tänkande</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
-          <t>KH4 Reproduktion och relationer; SU3 Informationsgranskning</t>
+          <t>Reproduktion och relationer; Informationsgranskning</t>
         </is>
       </c>
       <c r="M173" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -11151,17 +11151,17 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>S3 Evolution och världsbild; S2 Begrepp och samband</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>NM1 Evolution och mångfald; NM5 Fotosyntes, kretslopp, energi</t>
+          <t>Evolution och mångfald; Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="M174" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -11214,17 +11214,17 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>S7 Systematiska undersökningar</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
-          <t>SU1 Undersökningar</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="M175" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -11277,17 +11277,17 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>S4 Argument och kommunikation; S5 Etiska val</t>
+          <t>Formulera egna och granska andras argument; kommunicera; Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>SU4 Argumentation</t>
+          <t>Argumentation</t>
         </is>
       </c>
       <c r="M176" s="4" t="inlineStr">
         <is>
-          <t>F2 Granska/ta ställning</t>
+          <t>Granska/ta ställning</t>
         </is>
       </c>
     </row>
@@ -11340,17 +11340,17 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>S7 Systematiska undersökningar</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
-          <t>SU1 Undersökningar</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="M177" s="4" t="inlineStr">
         <is>
-          <t>F3 Undersöka</t>
+          <t>Undersöka</t>
         </is>
       </c>
     </row>
@@ -11399,17 +11399,17 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>KH1 Celler och organsystem; KH2 Infektioner; KH3 Hälsa</t>
+          <t>Celler och organsystem; Infektioner; Hälsa</t>
         </is>
       </c>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller</t>
+          <t>Begrepp/modeller</t>
         </is>
       </c>
     </row>
@@ -11458,13 +11458,13 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>S2 Begrepp och samband; S7 Systematiska undersökningar</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="L179" s="4" t="inlineStr"/>
       <c r="M179" s="4" t="inlineStr">
         <is>
-          <t>F1 Begrepp/modeller; F2 Granska/ta ställning; F3 Undersöka</t>
+          <t>Begrepp/modeller; Granska/ta ställning; Undersöka</t>
         </is>
       </c>
     </row>

--- a/planering/biologi-planering.xlsx
+++ b/planering/biologi-planering.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Täckning" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Moment'!$A$1:$M$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Moment'!$A$1:$L$179</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Delområden'!$A$1:$I$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Områden'!$A$1:$E$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Labbar (45 min)'!$A$1:$F$25</definedName>
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M179"/>
+  <dimension ref="A1:L179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -534,13 +534,12 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -576,35 +575,30 @@
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Moment nr</t>
+          <t>Moment</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>Moment</t>
+          <t>Innehåll i texten</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>Innehåll i texten</t>
+          <t>Begrepp</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Begrepp</t>
+          <t>Syfte</t>
         </is>
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Syfte</t>
+          <t>Centralt innehåll</t>
         </is>
       </c>
       <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Centralt innehåll</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Förmåga</t>
         </is>
@@ -639,35 +633,30 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1.1.1</t>
+          <t>Från fråga till plan</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>Från fråga till plan</t>
+          <t>Göra frågan undersökningsbar; förväntan/hypotes; oberoende, beroende och kontrollerade variabler; rättvist försök.</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Göra frågan undersökningsbar; förväntan/hypotes; oberoende, beroende och kontrollerade variabler; rättvist försök.</t>
+          <t>undersökningsbar fråga, hypotes, oberoende, beroende och kontrollerad variabel, rättvist försök</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>undersökningsbar fråga, hypotes, oberoende, beroende och kontrollerad variabel, rättvist försök</t>
+          <t>Nyfikenhet och intresse; ställa frågor om natur och människa utifrån egna upplevelser och aktuella händelser; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Nyfikenhet och intresse; ställa frågor om natur och människa utifrån egna upplevelser och aktuella händelser; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>Undersökningar</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -702,35 +691,30 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>Dokumentera: tabell, diagram, rapport</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Dokumentera: tabell, diagram, rapport</t>
+          <t>Rita tabell och diagram, välja diagramtyp, skriva en kort rapport med bilder.</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Rita tabell och diagram, välja diagramtyp, skriva en kort rapport med bilder.</t>
+          <t>tabell, diagram, rapport, axel, enhet</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>tabell, diagram, rapport, axel, enhet</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Undersökningar</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -765,35 +749,30 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>1.1.3</t>
+          <t>Värdera: slump, felkällor, slutsats</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Värdera: slump, felkällor, slutsats</t>
+          <t>Upprepade mätningar, felkällor, vad resultatet visar och inte visar; nytt försök.</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Upprepade mätningar, felkällor, vad resultatet visar och inte visar; nytt försök.</t>
+          <t>felkälla, slump, upprepning, giltighet, slutsats</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>felkälla, slump, upprepning, giltighet, slutsats</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>Undersökningar</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -828,35 +807,30 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>1.1.L</t>
+          <t>Reaktionstid som rättvist försök</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Reaktionstid som rättvist försök</t>
+          <t>Påverkar övning reaktionstiden? Varierar: antal försök. Mäter: fallsträcka med fallande linjal. Kontrollerar: hand, startläge, mätare. Planeras i lektionerna, utförs och dokumenteras i passet.</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Påverkar övning reaktionstiden? Varierar: antal försök. Mäter: fallsträcka med fallande linjal. Kontrollerar: hand, startläge, mätare. Planeras i lektionerna, utförs och dokumenteras i passet.</t>
+          <t>variabel, mätning, medelvärde, felkälla</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>variabel, mätning, medelvärde, felkälla</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder; Färdigheter i att hantera material, utrustning och digitala verktyg</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder; Färdigheter i att hantera material, utrustning och digitala verktyg</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>Undersökningar</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -889,29 +863,28 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Vad är biologi?</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Vad är biologi?</t>
+          <t>Vad som kännetecknar liv, biologins grenar, vad biologer jobbar med (fält, labb, data).</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Vad som kännetecknar liv, biologins grenar, vad biologer jobbar med (fält, labb, data).</t>
+          <t>biologi, liv, levande/icke-levande, cell, organism</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>biologi, liv, levande/icke-levande, cell, organism</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
           <t>Nyfikenhet och intresse; ställa frågor om natur och människa utifrån egna upplevelser och aktuella händelser; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -944,33 +917,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Från nyfikenhet till fråga</t>
+        </is>
+      </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Från nyfikenhet till fråga</t>
+          <t>Ställa frågor om natur och människa utifrån vardag och nyheter; göra om en fråga till en undersökningsbar fråga.</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Ställa frågor om natur och människa utifrån vardag och nyheter; göra om en fråga till en undersökningsbar fråga.</t>
+          <t>undersökningsbar fråga, observation, hypotes</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>undersökningsbar fråga, observation, hypotes</t>
+          <t>Nyfikenhet och intresse; ställa frågor om natur och människa utifrån egna upplevelser och aktuella händelser; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Nyfikenhet och intresse; ställa frågor om natur och människa utifrån egna upplevelser och aktuella händelser; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>Undersökningar</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -1003,33 +975,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Utföra: material, säkerhet, digitala verktyg</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Utföra: material, säkerhet, digitala verktyg</t>
+          <t>Labbsäkerhet, mikroskop, mätredskap, sensorer och kalkylblad; fältstudie kontra experiment.</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Labbsäkerhet, mikroskop, mätredskap, sensorer och kalkylblad; fältstudie kontra experiment.</t>
+          <t>mikroskop, mätinstrument, sensor, kalkylblad, riskbedömning</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>mikroskop, mätinstrument, sensor, kalkylblad, riskbedömning</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>Undersökningar</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -1064,35 +1035,30 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>1.2.1</t>
+          <t>Vad kan vetenskap pröva?</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Vad kan vetenskap pröva?</t>
+          <t>Påståenden som går/inte går att pröva, vad ett belägg är, skillnaden mot tro och åsikt, pseudovetenskap med exempel.</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Påståenden som går/inte går att pröva, vad ett belägg är, skillnaden mot tro och åsikt, pseudovetenskap med exempel.</t>
+          <t>belägg, påstående, pseudovetenskap, tro, åsikt</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>belägg, påstående, pseudovetenskap, tro, åsikt</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
+          <t>Informationsgranskning</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>Informationsgranskning</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -1127,35 +1093,30 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>När forskare ändrat sig</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>När forskare ändrat sig</t>
+          <t>Pasteur och spontan uppkomst, Semmelweis och handtvätt, magsårsbakterien: hur belägg ändrar bilden.</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Pasteur och spontan uppkomst, Semmelweis och handtvätt, magsårsbakterien: hur belägg ändrar bilden.</t>
+          <t>spontan uppkomst, mikroorganism, hygien</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>spontan uppkomst, mikroorganism, hygien</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Modeller och historia</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>Modeller och historia</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -1190,35 +1151,30 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>1.2.3</t>
+          <t>Söka information och bedöma källor</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Söka information och bedöma källor</t>
+          <t>Söksätt och olika typer av källor; trovärdighet och relevans: avsändare, syfte, reklam och vinklade rubriker.</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Söksätt och olika typer av källor; trovärdighet och relevans: avsändare, syfte, reklam och vinklade rubriker.</t>
+          <t>källa, sökord, trovärdighet, relevans, avsändare, syfte</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>källa, sökord, trovärdighet, relevans, avsändare, syfte</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
+          <t>Informationsgranskning</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>Informationsgranskning</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -1253,35 +1209,30 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>1.2.L</t>
+          <t>Granska ett påstående</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Granska ett påstående</t>
+          <t>Går ett vanligt hälsopåstående att belägga? Välj ett påstående, sök två källor och bedöm trovärdighet och relevans enligt en checklista.</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Går ett vanligt hälsopåstående att belägga? Välj ett påstående, sök två källor och bedöm trovärdighet och relevans enligt en checklista.</t>
+          <t>påstående, källa, trovärdighet, relevans</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>påstående, källa, trovärdighet, relevans</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
+          <t>Informationsgranskning</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>Informationsgranskning</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -1314,33 +1265,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Modeller och förklaringar</t>
+        </is>
+      </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Modeller och förklaringar</t>
+          <t>Vad en förklaringsmodell är och används till; modeller förenklar och kan förbättras.</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Vad en förklaringsmodell är och används till; modeller förenklar och kan förbättras.</t>
+          <t>modell, förklaringsmodell, teori</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>modell, förklaringsmodell, teori</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Modeller och historia</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>Modeller och historia</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -1373,33 +1323,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Upptäckter som ändrat vår syn på naturen</t>
+        </is>
+      </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Upptäckter som ändrat vår syn på naturen</t>
+          <t>Mikroskopet, evolutionsteorin och DNA som exempel på förändrad världsbild.</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Mikroskopet, evolutionsteorin och DNA som exempel på förändrad världsbild.</t>
+          <t>mikroskop, evolutionsteori, DNA</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>mikroskop, evolutionsteori, DNA</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
           <t>Modeller och historia</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1428,33 +1377,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Söka information</t>
+        </is>
+      </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Söka information</t>
+          <t>Söksätt, olika typer av källor (forskning, myndigheter, media, sociala medier), vem som står bakom.</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Söksätt, olika typer av källor (forskning, myndigheter, media, sociala medier), vem som står bakom.</t>
+          <t>källa, sökord, primär/sekundär källa</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>källa, sökord, primär/sekundär källa</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
+          <t>Informationsgranskning</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>Informationsgranskning</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -1487,33 +1435,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Statistik och diagram i påståenden</t>
+        </is>
+      </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Statistik och diagram i påståenden</t>
+          <t>Läsa diagram, samband och orsak, urval och stickprov, vilseledande diagram.</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Läsa diagram, samband och orsak, urval och stickprov, vilseledande diagram.</t>
+          <t>samband, orsak, stickprov, korrelation</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>samband, orsak, stickprov, korrelation</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
+          <t>Informationsgranskning; Undersökningar</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>Informationsgranskning; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -1546,33 +1493,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Argumentera</t>
+        </is>
+      </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Argumentera</t>
+          <t>Påstående, belägg, motargument och slutsats; skriftligt och muntligt.</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Påstående, belägg, motargument och slutsats; skriftligt och muntligt.</t>
+          <t>påstående, belägg, motargument, slutsats</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>påstående, belägg, motargument, slutsats</t>
+          <t>Formulera egna och granska andras argument; kommunicera</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Formulera egna och granska andras argument; kommunicera</t>
+          <t>Argumentation</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>Argumentation</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -1607,35 +1553,30 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2.1.1</t>
+          <t>Cellteorin och mikroskopet</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Cellteorin och mikroskopet</t>
+          <t>Alla organismer består av celler; hur mikroskopet visade cellen; storleksskala.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Alla organismer består av celler; hur mikroskopet visade cellen; storleksskala.</t>
+          <t>cellteori, mikroskop, förstoring</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>cellteori, mikroskop, förstoring</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem; Modeller och historia</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem; Modeller och historia</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -1670,35 +1611,30 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2.1.2</t>
+          <t>Djurcell och växtcell</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Djurcell och växtcell</t>
+          <t>Cellkärna, cellmembran, cytoplasma, mitokondrier, kloroplaster, cellvägg, vakuol.</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Cellkärna, cellmembran, cytoplasma, mitokondrier, kloroplaster, cellvägg, vakuol.</t>
+          <t>cellkärna, cellmembran, cytoplasma, mitokondrie, kloroplast, cellvägg, vakuol</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>cellkärna, cellmembran, cytoplasma, mitokondrie, kloroplast, cellvägg, vakuol</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -1733,35 +1669,30 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2.1.3</t>
+          <t>Bakterier och encelliga organismer</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Bakterier och encelliga organismer</t>
+          <t>Cell utan cellkärna, skillnader mot djur- och växtceller, encelliga organismer.</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Cell utan cellkärna, skillnader mot djur- och växtceller, encelliga organismer.</t>
+          <t>bakterie, encellig, cell utan cellkärna</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>bakterie, encellig, cell utan cellkärna</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -1796,35 +1727,30 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2.1.L</t>
+          <t>Mikroskopera celler</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Mikroskopera celler</t>
+          <t>Hur ser lök- och växtceller ut i mikroskop? Gör ett preparat, rita och märk cellen, jämför med en bild av djurcell.</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Hur ser lök- och växtceller ut i mikroskop? Gör ett preparat, rita och märk cellen, jämför med en bild av djurcell.</t>
+          <t>mikroskop, preparat, cellvägg, cellkärna</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>mikroskop, preparat, cellvägg, cellkärna</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Celler och organsystem; Undersökningar</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -1857,33 +1783,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Transport över cellmembranet</t>
+        </is>
+      </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Transport över cellmembranet</t>
+          <t>Diffusion och osmos med vardagsexempel och enkelt försök.</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Diffusion och osmos med vardagsexempel och enkelt försök.</t>
+          <t>diffusion, osmos, semipermeabelt membran</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>diffusion, osmos, semipermeabelt membran</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller; Undersöka</t>
         </is>
@@ -1916,33 +1841,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Gemensamt ursprung</t>
+        </is>
+      </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Gemensamt ursprung</t>
+          <t>Varför alla celler liknar varandra; cellens uppkomst ur andra celler som del av evolutionsbilden.</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Varför alla celler liknar varandra; cellens uppkomst ur andra celler som del av evolutionsbilden.</t>
+          <t>gemensam förfader, släktskap</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>gemensam förfader, släktskap</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
           <t>Evolution och mångfald</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1973,35 +1897,30 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>Växten som producent</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Växten som producent</t>
+          <t>Vad växten behöver och bildar; reaktionsformel i ord.</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Vad växten behöver och bildar; reaktionsformel i ord.</t>
+          <t>producent, fotosyntes, koldioxid, vatten, glukos, syre</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>producent, fotosyntes, koldioxid, vatten, glukos, syre</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -2036,35 +1955,30 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2.2.2</t>
+          <t>Cellandning</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Cellandning</t>
+          <t>Ämnen in/ut, mitokondrien, att alla levande celler andas, energi till livsfunktioner.</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Ämnen in/ut, mitokondrien, att alla levande celler andas, energi till livsfunktioner.</t>
+          <t>cellandning, mitokondrie, energi, syre</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>cellandning, mitokondrie, energi, syre</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Fotosyntes, kretslopp, energi; Celler och organsystem</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi; Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -2099,35 +2013,30 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>Processerna tillsammans</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Processerna tillsammans</t>
+          <t>Fotosyntes och cellandning som varandras motsatser; kol och energi i kretslopp.</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Fotosyntes och cellandning som varandras motsatser; kol och energi i kretslopp.</t>
+          <t>kretslopp, kol, energiflöde</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>kretslopp, kol, energiflöde</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -2162,35 +2071,30 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2.2.L</t>
+          <t>Jäst och koldioxid</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Jäst och koldioxid</t>
+          <t>Hur påverkar temperaturen jästens koldioxidbildning? Varierar: temperatur. Mäter: ballongens omfång eller skumhöjd efter fast tid.</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Hur påverkar temperaturen jästens koldioxidbildning? Varierar: temperatur. Mäter: ballongens omfång eller skumhöjd efter fast tid.</t>
+          <t>cellandning, jäsning, koldioxid, kontrollförsök</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>cellandning, jäsning, koldioxid, kontrollförsök</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Fotosyntes, kretslopp, energi; Undersökningar</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -2223,33 +2127,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Bladet och kloroplasten</t>
+        </is>
+      </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Bladet och kloroplasten</t>
+          <t>Bladets byggnad, klorofyll, klyvöppningar, var i cellen det sker.</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Bladets byggnad, klorofyll, klyvöppningar, var i cellen det sker.</t>
+          <t>klorofyll, kloroplast, klyvöppning</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>klorofyll, kloroplast, klyvöppning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Fotosyntes, kretslopp, energi; Celler och organsystem</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi; Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -2282,33 +2185,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Vad påverkar fotosyntesen?</t>
+        </is>
+      </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Vad påverkar fotosyntesen?</t>
+          <t>Ljus, koldioxid, temperatur; planera och genomföra ett försök.</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Ljus, koldioxid, temperatur; planera och genomföra ett försök.</t>
+          <t>ljusintensitet, temperatur, variabel</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>ljusintensitet, temperatur, variabel</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Fotosyntes, kretslopp, energi; Undersökningar</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -2341,33 +2243,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Från glukos till växtens kropp</t>
+        </is>
+      </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Från glukos till växtens kropp</t>
+          <t>Vad växten gör med sockret; energi lagras i kemiska bindningar.</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Vad växten gör med sockret; energi lagras i kemiska bindningar.</t>
+          <t>glukos, stärkelse, cellulosa, energirik</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>glukos, stärkelse, cellulosa, energirik</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -2400,33 +2301,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Jäsning</t>
+        </is>
+      </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Jäsning</t>
+          <t>Energi utan syre: jäst och mjölksyra; jämförelse med cellandning.</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Energi utan syre: jäst och mjölksyra; jämförelse med cellandning.</t>
+          <t>jäsning, jäst, mjölksyra, alkohol</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>jäsning, jäst, mjölksyra, alkohol</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -2461,35 +2361,30 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2.3.1</t>
+          <t>Specialiserade celler och vävnader</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Specialiserade celler och vävnader</t>
+          <t>Olika celltyper med olika uppgifter; vävnad och organ.</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Olika celltyper med olika uppgifter; vävnad och organ.</t>
+          <t>specialiserad cell, vävnad, organ</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>specialiserad cell, vävnad, organ</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -2524,35 +2419,30 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2.3.2</t>
+          <t>Kroppens organsystem – översikt</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Kroppens organsystem – översikt</t>
+          <t>Vilka system kroppen har och vad de gör, som karta över kommande kapitel.</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Vilka system kroppen har och vad de gör, som karta över kommande kapitel.</t>
+          <t>organsystem, organism</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>organsystem, organism</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -2585,33 +2475,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Växtens organ</t>
+        </is>
+      </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Växtens organ</t>
+          <t>Rot, stam, blad, blomma och deras uppgifter.</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Rot, stam, blad, blomma och deras uppgifter.</t>
+          <t>rot, stam, blad, blomma</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>rot, stam, blad, blomma</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -2646,35 +2535,30 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>3.1.1</t>
+          <t>Gener, arter och ekosystem</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Gener, arter och ekosystem</t>
+          <t>De tre nivåerna med exempel.</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>De tre nivåerna med exempel.</t>
+          <t>biologisk mångfald, genetisk variation, artmångfald, ekosystemmångfald</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>biologisk mångfald, genetisk variation, artmångfald, ekosystemmångfald</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald; Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald; Påverkan och hållbarhet</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -2709,35 +2593,30 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>3.1.2</t>
+          <t>Ekosystemtjänster</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Ekosystemtjänster</t>
+          <t>Försörjande, reglerande, kulturella och stödjande tjänster med exempel.</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Försörjande, reglerande, kulturella och stödjande tjänster med exempel.</t>
+          <t>ekosystemtjänst, försörjande, reglerande, kulturell, stödjande</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>ekosystemtjänst, försörjande, reglerande, kulturell, stödjande</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>Påverkan och hållbarhet</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -2772,35 +2651,30 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>3.1.3</t>
+          <t>Hoten mot mångfalden</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Hoten mot mångfalden</t>
+          <t>Förlorade livsmiljöer, överutnyttjande, invasiva arter, klimat, föroreningar.</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Förlorade livsmiljöer, överutnyttjande, invasiva arter, klimat, föroreningar.</t>
+          <t>habitatförlust, invasiv art, överexploatering</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>habitatförlust, invasiv art, överexploatering</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>Påverkan och hållbarhet</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -2835,35 +2709,30 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>3.1.L</t>
+          <t>Artinventering i en provruta</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Artinventering i en provruta</t>
+          <t>Hur många sorters växter finns i en kvadratmeter? Räkna olika sorter i provrutor på två platser, jämför i tabell.</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Hur många sorters växter finns i en kvadratmeter? Räkna olika sorter i provrutor på två platser, jämför i tabell.</t>
+          <t>inventering, provruta, artantal</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>inventering, provruta, artantal</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Påverkan och hållbarhet; Undersökningar</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>Påverkan och hållbarhet; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -2896,33 +2765,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Hur mäter man mångfald?</t>
+        </is>
+      </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Hur mäter man mångfald?</t>
+          <t>Artantal, inventering, tabell och diagram.</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Artantal, inventering, tabell och diagram.</t>
+          <t>inventering, artantal</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>inventering, artantal</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Påverkan och hållbarhet; Undersökningar</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>Påverkan och hållbarhet; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -2955,33 +2823,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Var finns mångfalden?</t>
+        </is>
+      </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Var finns mångfalden?</t>
+          <t>Regnskog, korallrev, Sveriges naturtyper; varför vissa platser har fler arter.</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Regnskog, korallrev, Sveriges naturtyper; varför vissa platser har fler arter.</t>
+          <t>naturtyp, regnskog, korallrev</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>naturtyp, regnskog, korallrev</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald; Ekosystem och populationer</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald; Ekosystem och populationer</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -3016,35 +2883,30 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>3.2.1</t>
+          <t>Rikena</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Rikena</t>
+          <t>Djur, växter, svampar, bakterier och encelliga organismer.</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Djur, växter, svampar, bakterier och encelliga organismer.</t>
+          <t>rike: djur, växter, svampar, bakterier</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>rike: djur, växter, svampar, bakterier</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -3079,35 +2941,30 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>3.2.2</t>
+          <t>Bestämningsnycklar</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Bestämningsnycklar</t>
+          <t>Hur man använder och bygger en nyckel.</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Hur man använder och bygger en nyckel.</t>
+          <t>bestämningsnyckel, kännetecken</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>bestämningsnyckel, kännetecken</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>Undersökningar</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -3142,35 +2999,30 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>3.2.3</t>
+          <t>Anpassningar</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Anpassningar</t>
+          <t>Hur byggnad och beteende passar miljön; ett första möte med naturligt urval.</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Hur byggnad och beteende passar miljön; ett första möte med naturligt urval.</t>
+          <t>anpassning, variation, naturligt urval</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>anpassning, variation, naturligt urval</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald</t>
-        </is>
-      </c>
-      <c r="M43" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -3205,35 +3057,30 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>3.2.L</t>
+          <t>Artbestämning med nyckel</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Artbestämning med nyckel</t>
+          <t>Vilka arter är det? Bestäm med nyckel. Bestäm löv eller barr med bestämningsnyckel och dokumentera med bild.</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Vilka arter är det? Bestäm med nyckel. Bestäm löv eller barr med bestämningsnyckel och dokumentera med bild.</t>
+          <t>bestämningsnyckel, kännetecken, art</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>bestämningsnyckel, kännetecken, art</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Evolution och mångfald; Undersökningar</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M44" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -3266,33 +3113,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Varför gruppera?</t>
+        </is>
+      </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Varför gruppera?</t>
+          <t>Art, släkte, familj med exempel; vetenskapliga namn.</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Art, släkte, familj med exempel; vetenskapliga namn.</t>
+          <t>art, släkte, familj, vetenskapligt namn</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>art, släkte, familj, vetenskapligt namn</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald</t>
-        </is>
-      </c>
-      <c r="M45" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -3325,33 +3171,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Vanliga svenska arter</t>
+        </is>
+      </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Vanliga svenska arter</t>
+          <t>Ett urval växter, svampar, djur att känna igen.</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Ett urval växter, svampar, djur att känna igen.</t>
+          <t>art, igenkänning, utbredning</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>art, igenkänning, utbredning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald</t>
-        </is>
-      </c>
-      <c r="M46" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -3384,33 +3229,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Alger, mossor och ormbunkar</t>
+        </is>
+      </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Alger, mossor och ormbunkar</t>
+          <t>Sporväxter, deras livscykel i grova drag och var de lever.</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Sporväxter, deras livscykel i grova drag och var de lever.</t>
+          <t>alger, mossor, ormbunkar, sporer</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>alger, mossor, ormbunkar, sporer</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald</t>
-        </is>
-      </c>
-      <c r="M47" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -3443,33 +3287,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Fröväxter</t>
+        </is>
+      </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Fröväxter</t>
+          <t>Barrväxter och blomväxter; pollinering och spridning.</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>Barrväxter och blomväxter; pollinering och spridning.</t>
+          <t>barrväxter, blomväxter, pollinering, frö</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>barrväxter, blomväxter, pollinering, frö</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald</t>
-        </is>
-      </c>
-      <c r="M48" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -3502,33 +3345,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>Svampar och lavar</t>
+        </is>
+      </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Svampar och lavar</t>
+          <t>Nedbrytare, mykorrhiza och lavens samarbete.</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>Nedbrytare, mykorrhiza och lavens samarbete.</t>
+          <t>svamp, mycel, nedbrytare, lav, symbios</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>svamp, mycel, nedbrytare, lav, symbios</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald; Ekosystem och populationer</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald; Ekosystem och populationer</t>
-        </is>
-      </c>
-      <c r="M49" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -3561,33 +3403,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Ryggradslösa djur</t>
+        </is>
+      </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>Ryggradslösa djur</t>
+          <t>Leddjur, blötdjur, maskar m.fl.; mångfald.</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Leddjur, blötdjur, maskar m.fl.; mångfald.</t>
+          <t>leddjur, blötdjur, maskar</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>leddjur, blötdjur, maskar</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald</t>
-        </is>
-      </c>
-      <c r="M50" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -3620,33 +3461,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Ryggradsdjur</t>
+        </is>
+      </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Ryggradsdjur</t>
+          <t>Fiskar, groddjur, kräldjur, fåglar, däggdjur.</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>Fiskar, groddjur, kräldjur, fåglar, däggdjur.</t>
+          <t>ryggrad, däggdjur, fåglar, groddjur, kräldjur, fiskar</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>ryggrad, däggdjur, fåglar, groddjur, kräldjur, fiskar</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald</t>
-        </is>
-      </c>
-      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -3681,35 +3521,30 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>Vad är ett ekosystem?</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Vad är ett ekosystem?</t>
+          <t>Levande och icke-levande delar; gränser och exempel.</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Levande och icke-levande delar; gränser och exempel.</t>
+          <t>ekosystem, biotisk, abiotisk, population</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>ekosystem, biotisk, abiotisk, population</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Ekosystem och populationer</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>Ekosystem och populationer</t>
-        </is>
-      </c>
-      <c r="M52" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -3744,35 +3579,30 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>4.1.2</t>
+          <t>Producenter, konsumenter och näringsvävar</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Producenter, konsumenter och näringsvävar</t>
+          <t>Roller i ekosystemet; rita och läsa näringskedjor och näringsvävar.</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Roller i ekosystemet; rita och läsa näringskedjor och näringsvävar.</t>
+          <t>producent, konsument, nedbrytare, näringskedja, näringsväv, trofinivå</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>producent, konsument, nedbrytare, näringskedja, näringsväv, trofinivå</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Ekosystem och populationer; Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>Ekosystem och populationer; Fotosyntes, kretslopp, energi</t>
-        </is>
-      </c>
-      <c r="M53" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -3807,35 +3637,30 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>4.1.3</t>
+          <t>Energiflöde och biomassa</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Energiflöde och biomassa</t>
+          <t>Energin minskar uppåt; varför det finns färre rovdjur än växtätare.</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Energin minskar uppåt; varför det finns färre rovdjur än växtätare.</t>
+          <t>energiflöde, biomassa, energiförlust</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>energiflöde, biomassa, energiförlust</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi</t>
-        </is>
-      </c>
-      <c r="M54" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -3870,35 +3695,30 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>4.1.L</t>
+          <t>Energi i en näringskedja – modellspel</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Energi i en näringskedja – modellspel</t>
+          <t>Hur mycket energi når toppen av en kedja? Modell med kort och marker: energi minskar mellan nivåerna; noteras i tabell.</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>Hur mycket energi når toppen av en kedja? Modell med kort och marker: energi minskar mellan nivåerna; noteras i tabell.</t>
+          <t>energiförlust, trofinivå, modell</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>energiförlust, trofinivå, modell</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Fotosyntes, kretslopp, energi; Undersökningar</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -3931,33 +3751,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Lokala och globala ekosystem</t>
+        </is>
+      </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Lokala och globala ekosystem</t>
+          <t>Skog, sjö, hav, fjäll, och världens större naturtyper.</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>Skog, sjö, hav, fjäll, och världens större naturtyper.</t>
+          <t>skog, sjö, hav, biom</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>skog, sjö, hav, biom</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Ekosystem och populationer</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>Ekosystem och populationer</t>
-        </is>
-      </c>
-      <c r="M56" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -3990,33 +3809,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Habitat och nisch</t>
+        </is>
+      </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Habitat och nisch</t>
+          <t>Var och hur en art lever; två arter, samma miljö.</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>Var och hur en art lever; två arter, samma miljö.</t>
+          <t>habitat, nisch, konkurrens</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>habitat, nisch, konkurrens</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Ekosystem och populationer</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>Ekosystem och populationer</t>
-        </is>
-      </c>
-      <c r="M57" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -4049,33 +3867,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Producenter, konsumenter och nedbrytare</t>
+        </is>
+      </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Producenter, konsumenter och nedbrytare</t>
+          <t>Roller i ekosystemet.</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>Roller i ekosystemet.</t>
+          <t>producent, konsument, nedbrytare, växtätare, rovdjur</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>producent, konsument, nedbrytare, växtätare, rovdjur</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Ekosystem och populationer; Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>Ekosystem och populationer; Fotosyntes, kretslopp, energi</t>
-        </is>
-      </c>
-      <c r="M58" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -4108,29 +3925,28 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Störs vävan – vad händer?</t>
+        </is>
+      </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Störs vävan – vad händer?</t>
+          <t>Resonera om ett bortfall av en art.</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>Resonera om ett bortfall av en art.</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
           <t>nyckelart, följdeffekt</t>
         </is>
       </c>
-      <c r="K59" s="4" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>Ekosystem och populationer</t>
+        </is>
+      </c>
       <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>Ekosystem och populationer</t>
-        </is>
-      </c>
-      <c r="M59" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -4165,35 +3981,30 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>Materia tillverkas inte och försvinner inte</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>Materia tillverkas inte och försvinner inte</t>
+          <t>Atomerna återanvänds; kretslopp och energiflöde skiljs åt.</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>Atomerna återanvänds; kretslopp och energiflöde skiljs åt.</t>
+          <t>kretslopp, materia, atom, energiflöde</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>kretslopp, materia, atom, energiflöde</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi</t>
-        </is>
-      </c>
-      <c r="M60" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -4228,35 +4039,30 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>4.2.2</t>
+          <t>Kolets kretslopp</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Kolets kretslopp</t>
+          <t>Fotosyntes, cellandning, förbränning, fossilt kol.</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>Fotosyntes, cellandning, förbränning, fossilt kol.</t>
+          <t>kolets kretslopp, förbränning, fossilt kol</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>kolets kretslopp, förbränning, fossilt kol</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi</t>
-        </is>
-      </c>
-      <c r="M61" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -4291,35 +4097,30 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>4.2.3</t>
+          <t>Nedbrytning</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>Nedbrytning</t>
+          <t>Nedbrytarnas roll; jordens bildning.</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>Nedbrytarnas roll; jordens bildning.</t>
+          <t>nedbrytning, humus, mull</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>nedbrytning, humus, mull</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi</t>
-        </is>
-      </c>
-      <c r="M62" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -4354,35 +4155,30 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>4.2.L</t>
+          <t>Nedbrytning i jord</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Nedbrytning i jord</t>
+          <t>Hur snabbt bryts olika material ned? Starta ett försök med olika material i jord; avläs vid nästa pass.</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>Hur snabbt bryts olika material ned? Starta ett försök med olika material i jord; avläs vid nästa pass.</t>
+          <t>nedbrytning, nedbrytare, kontroll</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>nedbrytning, nedbrytare, kontroll</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Fotosyntes, kretslopp, energi; Undersökningar</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M63" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -4415,33 +4211,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Kvävets och vattnets kretslopp</t>
+        </is>
+      </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>Kvävets och vattnets kretslopp</t>
+          <t>Kvävefixering, växternas upptag, vattnets väg genom organismer.</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>Kvävefixering, växternas upptag, vattnets väg genom organismer.</t>
+          <t>kvävefixering, nitrat, vattnets kretslopp</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>kvävefixering, nitrat, vattnets kretslopp</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi</t>
-        </is>
-      </c>
-      <c r="M64" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -4476,35 +4271,30 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>4.3.1</t>
+          <t>Populationer och förändring</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Populationer och förändring</t>
+          <t>Födelser, dödsfall, in- och utvandring; tillväxtkurvor.</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>Födelser, dödsfall, in- och utvandring; tillväxtkurvor.</t>
+          <t>population, födelse, död, inflyttning, utflyttning</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>population, födelse, död, inflyttning, utflyttning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Ekosystem och populationer; Undersökningar</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>Ekosystem och populationer; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M65" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -4539,35 +4329,30 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>4.3.2</t>
+          <t>Begränsande faktorer</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>Begränsande faktorer</t>
+          <t>Föda, plats, sjukdom; bärkraft.</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>Föda, plats, sjukdom; bärkraft.</t>
+          <t>begränsande faktor, bärkraft, resurs</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>begränsande faktor, bärkraft, resurs</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Ekosystem och populationer</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>Ekosystem och populationer</t>
-        </is>
-      </c>
-      <c r="M66" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -4602,35 +4387,30 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>4.3.3</t>
+          <t>Konkurrens, jakt och samarbete</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Konkurrens, jakt och samarbete</t>
+          <t>Predation, parasitism, symbios; samutveckling som exempel på evolution.</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>Predation, parasitism, symbios; samutveckling som exempel på evolution.</t>
+          <t>predation, parasitism, symbios, samutveckling</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>predation, parasitism, symbios, samutveckling</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Ekosystem och populationer; Evolution och mångfald</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>Ekosystem och populationer; Evolution och mångfald</t>
-        </is>
-      </c>
-      <c r="M67" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -4665,35 +4445,30 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>4.3.L</t>
+          <t>Rovdjur–bytesmodell</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>Rovdjur–bytesmodell</t>
+          <t>Hur påverkar tillgången på föda en population? Modellspel med kort; ändra födomängd och notera populationen i tabell och diagram.</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>Hur påverkar tillgången på föda en population? Modellspel med kort; ändra födomängd och notera populationen i tabell och diagram.</t>
+          <t>population, begränsande faktor, bärkraft</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>population, begränsande faktor, bärkraft</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Ekosystem och populationer; Undersökningar</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>Ekosystem och populationer; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M68" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -4726,33 +4501,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>Ekosystems känslighet</t>
+        </is>
+      </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Ekosystems känslighet</t>
+          <t>Nyckelarter, störningar, återhämtning.</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>Nyckelarter, störningar, återhämtning.</t>
+          <t>stabilitet, störning, återhämtning</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>stabilitet, störning, återhämtning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Ekosystem och populationer</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>Ekosystem och populationer</t>
-        </is>
-      </c>
-      <c r="M69" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -4787,35 +4561,30 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>Övergödning</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Övergödning</t>
+          <t>Orsaker och följder, exemplet Östersjön.</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>Orsaker och följder, exemplet Östersjön.</t>
+          <t>övergödning, fosfor, kväve, algblomning, syrebrist</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>övergödning, fosfor, kväve, algblomning, syrebrist</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>Påverkan och hållbarhet</t>
-        </is>
-      </c>
-      <c r="M70" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -4850,35 +4619,30 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>5.1.2</t>
+          <t>Växthuseffekten</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Växthuseffekten</t>
+          <t>Naturlig och förstärkt växthuseffekt.</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>Naturlig och förstärkt växthuseffekt.</t>
+          <t>växthuseffekt, växthusgas, global uppvärmning</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>växthuseffekt, växthusgas, global uppvärmning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Fotosyntes, kretslopp, energi; Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi; Påverkan och hållbarhet</t>
-        </is>
-      </c>
-      <c r="M71" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -4913,35 +4677,30 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>5.1.3</t>
+          <t>Följder för arter och ekosystem</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>Följder för arter och ekosystem</t>
+          <t>Förändrade utbredningsområden, korallblekning, havsförsurning.</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>Förändrade utbredningsområden, korallblekning, havsförsurning.</t>
+          <t>utbredningsområde, havsförsurning</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>utbredningsområde, havsförsurning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>Påverkan och hållbarhet</t>
-        </is>
-      </c>
-      <c r="M72" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -4976,35 +4735,30 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>5.1.L</t>
+          <t>Växthuseffekten – modell</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Växthuseffekten – modell</t>
+          <t>Hur påverkar en 'atmosfär' temperaturen? Två flaskor med termometer under lampa, den ena med lock. Modellen förenklar verkligheten.</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>Hur påverkar en 'atmosfär' temperaturen? Två flaskor med termometer under lampa, den ena med lock. Modellen förenklar verkligheten.</t>
+          <t>växthuseffekt, modell, mätning</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>växthuseffekt, modell, mätning</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Fotosyntes, kretslopp, energi; Påverkan och hållbarhet; Undersökningar</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi; Påverkan och hållbarhet; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M73" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -5037,33 +4791,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Naturbruk</t>
+        </is>
+      </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>Naturbruk</t>
+          <t>Jordbruk, skogsbruk och fiske; nytta och påverkan.</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>Jordbruk, skogsbruk och fiske; nytta och påverkan.</t>
+          <t>naturbruk, jordbruk, skogsbruk, fiske</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>naturbruk, jordbruk, skogsbruk, fiske</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>Påverkan och hållbarhet</t>
-        </is>
-      </c>
-      <c r="M74" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -5096,33 +4849,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr"/>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>Miljögifter och bioackumulering</t>
+        </is>
+      </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Miljögifter och bioackumulering</t>
+          <t>Hur ämnen sprids och ansamlas i näringskedjan.</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>Hur ämnen sprids och ansamlas i näringskedjan.</t>
+          <t>miljögift, bioackumulering</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>miljögift, bioackumulering</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Påverkan och hållbarhet; Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>Påverkan och hållbarhet; Fotosyntes, kretslopp, energi</t>
-        </is>
-      </c>
-      <c r="M75" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -5155,33 +4907,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Försurning och invasiva arter</t>
+        </is>
+      </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>Försurning och invasiva arter</t>
+          <t>Orsaker, följder och åtgärder.</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>Orsaker, följder och åtgärder.</t>
+          <t>försurning, invasiv art, utsläpp</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>försurning, invasiv art, utsläpp</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>Påverkan och hållbarhet</t>
-        </is>
-      </c>
-      <c r="M76" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -5214,29 +4965,28 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G77" s="4" t="inlineStr"/>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>Kolsänkor och åtgärder</t>
+        </is>
+      </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Kolsänkor och åtgärder</t>
+          <t>Skog, hav, mark; vad som minskar utsläpp.</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>Skog, hav, mark; vad som minskar utsläpp.</t>
-        </is>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
           <t>kolsänka, utsläppsminskning</t>
         </is>
       </c>
-      <c r="K77" s="4" t="inlineStr"/>
+      <c r="J77" s="4" t="inlineStr"/>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>Fotosyntes, kretslopp, energi; Påverkan och hållbarhet</t>
+        </is>
+      </c>
       <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>Fotosyntes, kretslopp, energi; Påverkan och hållbarhet</t>
-        </is>
-      </c>
-      <c r="M77" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -5271,35 +5021,30 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>5.2.1</t>
+          <t>Vad är hållbar utveckling?</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>Vad är hållbar utveckling?</t>
+          <t>Ekologisk, social och ekonomisk dimension.</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>Ekologisk, social och ekonomisk dimension.</t>
+          <t>hållbar utveckling, ekologisk, social och ekonomisk hållbarhet</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>hållbar utveckling, ekologisk, social och ekonomisk hållbarhet</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>Påverkan och hållbarhet</t>
-        </is>
-      </c>
-      <c r="M78" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -5334,35 +5079,30 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>5.2.2</t>
+          <t>Naturresurser och ekosystemtjänster</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Naturresurser och ekosystemtjänster</t>
+          <t>Förnybart och icke-förnybart; vad vi får gratis av naturen.</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>Förnybart och icke-förnybart; vad vi får gratis av naturen.</t>
+          <t>naturresurs, förnybar, icke-förnybar, ekosystemtjänst</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>naturresurs, förnybar, icke-förnybar, ekosystemtjänst</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>Påverkan och hållbarhet</t>
-        </is>
-      </c>
-      <c r="M79" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -5397,35 +5137,30 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>5.2.3</t>
+          <t>Vad kan jag och samhället göra?</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>Vad kan jag och samhället göra?</t>
+          <t>Konsumtion, mat, resor, lagar och naturskydd.</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>Konsumtion, mat, resor, lagar och naturskydd.</t>
+          <t>konsumtion, ekologiskt fotavtryck, naturskydd</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>konsumtion, ekologiskt fotavtryck, naturskydd</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
+          <t>Påverkan och hållbarhet</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>Påverkan och hållbarhet</t>
-        </is>
-      </c>
-      <c r="M80" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -5460,35 +5195,30 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>5.2.L</t>
+          <t>Argumentera i en miljöfråga</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Argumentera i en miljöfråga</t>
+          <t>Hur kan vi väga naturvetenskapliga och etiska skäl? Strukturerad diskussion med roller; samla belägg och bemöt motargument.</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>Hur kan vi väga naturvetenskapliga och etiska skäl? Strukturerad diskussion med roller; samla belägg och bemöt motargument.</t>
+          <t>argument, motargument, ståndpunkt</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>argument, motargument, ståndpunkt</t>
+          <t>Formulera egna och granska andras argument; kommunicera; Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>Formulera egna och granska andras argument; kommunicera; Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
+          <t>Argumentation</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>Argumentation</t>
-        </is>
-      </c>
-      <c r="M81" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -5521,33 +5251,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G82" s="4" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Argumentera i en miljöfråga</t>
+        </is>
+      </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>Argumentera i en miljöfråga</t>
+          <t>Samla belägg, bemöta motargument, ta ställning.</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>Samla belägg, bemöta motargument, ta ställning.</t>
+          <t>argument, ståndpunkt, intressekonflikt</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>argument, ståndpunkt, intressekonflikt</t>
+          <t>Formulera egna och granska andras argument; kommunicera; Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>Formulera egna och granska andras argument; kommunicera; Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
+          <t>Argumentation</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>Argumentation</t>
-        </is>
-      </c>
-      <c r="M82" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -5582,35 +5311,30 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>6.1.1</t>
+          <t>Kolhydrater, proteiner och fetter</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Kolhydrater, proteiner och fetter</t>
+          <t>Uppgifter och källor.</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>Uppgifter och källor.</t>
+          <t>kolhydrat, protein, fett, aminosyra</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>kolhydrat, protein, fett, aminosyra</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem; Hälsa</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem; Hälsa</t>
-        </is>
-      </c>
-      <c r="M83" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -5645,35 +5369,30 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>Matens väg och spjälkning</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>Matens väg och spjälkning</t>
+          <t>Matspjälkningens organ från mun till tjocktarm; enzymer och upptag i tunntarmen.</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>Matspjälkningens organ från mun till tjocktarm; enzymer och upptag i tunntarmen.</t>
+          <t>matstrupe, magsäck, tunntarm, tjocktarm, enzym, spjälkning, upptag</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>matstrupe, magsäck, tunntarm, tjocktarm, enzym, spjälkning, upptag</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M84" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -5708,35 +5427,30 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>6.1.3</t>
+          <t>Kostråd och energibalans</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Kostråd och energibalans</t>
+          <t>Vad kostråd bygger på; vad som händer vid över- och underskott.</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>Vad kostråd bygger på; vad som händer vid över- och underskott.</t>
+          <t>kostråd, energibalans, näringsrik</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>kostråd, energibalans, näringsrik</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa</t>
-        </is>
-      </c>
-      <c r="M85" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -5771,35 +5485,30 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>6.1.L</t>
+          <t>Enzymförsök</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Enzymförsök</t>
+          <t>Hur påverkar temperatur nedbrytning av stärkelse? Varierar: temperatur. Mäter: tid tills jodtestet inte längre ger färg.</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>Hur påverkar temperatur nedbrytning av stärkelse? Varierar: temperatur. Mäter: tid tills jodtestet inte längre ger färg.</t>
+          <t>enzym, stärkelse, jodtest</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>enzym, stärkelse, jodtest</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Celler och organsystem; Undersökningar</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M86" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -5832,33 +5541,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G87" s="4" t="inlineStr"/>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>Vitaminer, mineraler, vatten och fibrer</t>
+        </is>
+      </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Vitaminer, mineraler, vatten och fibrer</t>
+          <t>Vad kroppen behöver i små mängder.</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>Vad kroppen behöver i små mängder.</t>
+          <t>vitamin, mineral, fiber, vatten</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>vitamin, mineral, fiber, vatten</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem; Hälsa</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem; Hälsa</t>
-        </is>
-      </c>
-      <c r="M87" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -5891,33 +5599,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>Energi i maten</t>
+        </is>
+      </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Energi i maten</t>
+          <t>Energiinnehåll och energibehov.</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>Energiinnehåll och energibehov.</t>
+          <t>energi, kilojoule, energibehov</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>energi, kilojoule, energibehov</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa</t>
-        </is>
-      </c>
-      <c r="M88" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -5950,33 +5657,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G89" s="4" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>Enzymer och spjälkning</t>
+        </is>
+      </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Enzymer och spjälkning</t>
+          <t>Vad enzymer gör; vad som påverkar dem.</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>Vad enzymer gör; vad som påverkar dem.</t>
+          <t>enzym, spjälkning, substrat</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>enzym, spjälkning, substrat</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M89" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -6009,33 +5715,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>Upptag och tarmflora</t>
+        </is>
+      </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>Upptag och tarmflora</t>
+          <t>Tunntarmens yta; tarmbakteriernas roll.</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>Tunntarmens yta; tarmbakteriernas roll.</t>
+          <t>upptag, tarmludd, tarmflora</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>upptag, tarmludd, tarmflora</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem; Infektioner</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem; Infektioner</t>
-        </is>
-      </c>
-      <c r="M90" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -6068,29 +5773,28 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G91" s="4" t="inlineStr"/>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>Mat och miljö</t>
+        </is>
+      </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Mat och miljö</t>
+          <t>Matens klimat- och naturpåverkan.</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>Matens klimat- och naturpåverkan.</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
           <t>klimatpåverkan, matproduktion</t>
         </is>
       </c>
-      <c r="K91" s="4" t="inlineStr"/>
+      <c r="J91" s="4" t="inlineStr"/>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>Hälsa; Påverkan och hållbarhet</t>
+        </is>
+      </c>
       <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa; Påverkan och hållbarhet</t>
-        </is>
-      </c>
-      <c r="M91" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -6123,33 +5827,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>Granska kostpåståenden</t>
+        </is>
+      </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>Granska kostpåståenden</t>
+          <t>Dieter, kosttillskott, influerare.</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>Dieter, kosttillskott, influerare.</t>
+          <t>kosttillskott, påstående, belägg</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>kosttillskott, påstående, belägg</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan; Formulera egna och granska andras argument; kommunicera</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan; Formulera egna och granska andras argument; kommunicera</t>
+          <t>Hälsa; Informationsgranskning; Argumentation</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa; Informationsgranskning; Argumentation</t>
-        </is>
-      </c>
-      <c r="M92" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -6184,35 +5887,30 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>6.2.1</t>
+          <t>Luftvägar och lungor</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Luftvägar och lungor</t>
+          <t>Näsa till lungblåsor; gasutbyte.</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>Näsa till lungblåsor; gasutbyte.</t>
+          <t>luftstrupe, bronker, lungblåsor, gasutbyte</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>luftstrupe, bronker, lungblåsor, gasutbyte</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M93" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -6247,35 +5945,30 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>6.2.2</t>
+          <t>Hjärta och blodkärl</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Hjärta och blodkärl</t>
+          <t>Hjärtats byggnad, artärer, vener, kapillärer.</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>Hjärtats byggnad, artärer, vener, kapillärer.</t>
+          <t>hjärta, förmak, kammare, klaff, artär, ven, kapillär</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>hjärta, förmak, kammare, klaff, artär, ven, kapillär</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M94" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -6310,35 +6003,30 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>6.2.3</t>
+          <t>Blodomloppet och syretransport</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Blodomloppet och syretransport</t>
+          <t>Lilla och stora kretsloppet.</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>Lilla och stora kretsloppet.</t>
+          <t>lilla och stora kretsloppet, syretransport</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>lilla och stora kretsloppet, syretransport</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M95" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -6373,35 +6061,30 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>6.2.L</t>
+          <t>Puls och andning vid belastning</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>Puls och andning vid belastning</t>
+          <t>Hur förändras puls och andning efter ansträngning? Mät vila och efter belastning; sammanställ i diagram.</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>Hur förändras puls och andning efter ansträngning? Mät vila och efter belastning; sammanställ i diagram.</t>
+          <t>puls, andningsfrekvens, belastning</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>puls, andningsfrekvens, belastning</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Celler och organsystem; Hälsa; Undersökningar</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem; Hälsa; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M96" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -6434,33 +6117,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>Andning och cellandning</t>
+        </is>
+      </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Andning och cellandning</t>
+          <t>Kopplingen mellan lungorna och cellernas behov.</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>Kopplingen mellan lungorna och cellernas behov.</t>
+          <t>cellandning, syre, koldioxid</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>cellandning, syre, koldioxid</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem; Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem; Fotosyntes, kretslopp, energi</t>
-        </is>
-      </c>
-      <c r="M97" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -6493,33 +6175,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G98" s="4" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Blodet</t>
+        </is>
+      </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>Blodet</t>
+          <t>Röda och vita blodkroppar, blodplättar, plasma.</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>Röda och vita blodkroppar, blodplättar, plasma.</t>
+          <t>röda och vita blodkroppar, blodplättar, plasma, hemoglobin</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>röda och vita blodkroppar, blodplättar, plasma, hemoglobin</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M98" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -6552,33 +6233,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G99" s="4" t="inlineStr"/>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>Skelett och muskler</t>
+        </is>
+      </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>Skelett och muskler</t>
+          <t>Uppgifter och samarbete i rörelse.</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>Uppgifter och samarbete i rörelse.</t>
+          <t>skelett, led, muskel, sena</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>skelett, led, muskel, sena</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M99" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -6611,33 +6291,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>Samverkan vid ansträngning</t>
+        </is>
+      </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>Samverkan vid ansträngning</t>
+          <t>Andning, puls och blodflöde.</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>Andning, puls och blodflöde.</t>
+          <t>puls, andningsfrekvens, samverkan</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>puls, andningsfrekvens, samverkan</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem; Hälsa</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem; Hälsa</t>
-        </is>
-      </c>
-      <c r="M100" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -6672,35 +6351,30 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>7.1.1</t>
+          <t>Bakterier och virus</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Bakterier och virus</t>
+          <t>Byggnad och förökning; nyttiga och skadliga bakterier; virus i värdceller; vad som skiljer dem åt.</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>Byggnad och förökning; nyttiga och skadliga bakterier; virus i värdceller; vad som skiljer dem åt.</t>
+          <t>bakterie, virus, värdcell, delning, förökning</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>bakterie, virus, värdcell, delning, förökning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>Infektioner</t>
-        </is>
-      </c>
-      <c r="M101" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -6735,35 +6409,30 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>7.1.2</t>
+          <t>Smittvägar</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>Smittvägar</t>
+          <t>Droppe, kontakt, mat, vektorer.</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>Droppe, kontakt, mat, vektorer.</t>
+          <t>smittväg, droppsmitta, kontaktsmitta, vektor</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>smittväg, droppsmitta, kontaktsmitta, vektor</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>Infektioner</t>
-        </is>
-      </c>
-      <c r="M102" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -6798,35 +6467,30 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>7.1.3</t>
+          <t>Förebygga smitta</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>Förebygga smitta</t>
+          <t>Hygien, isolering, smittspårning; epidemi och pandemi.</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>Hygien, isolering, smittspårning; epidemi och pandemi.</t>
+          <t>hygien, epidemi, pandemi, smittspårning</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>hygien, epidemi, pandemi, smittspårning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Infektioner; Hälsa</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>Infektioner; Hälsa</t>
-        </is>
-      </c>
-      <c r="M103" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -6861,35 +6525,30 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>7.1.L</t>
+          <t>Smittspridningsmodell med handtvätt</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>Smittspridningsmodell med handtvätt</t>
+          <t>Hur snabbt sprids smitta, och hur påverkar handtvätt? Modellmaterial (glitter eller fluorescerande pulver) med och utan handtvätt; räkna 'smittade'.</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>Hur snabbt sprids smitta, och hur påverkar handtvätt? Modellmaterial (glitter eller fluorescerande pulver) med och utan handtvätt; räkna 'smittade'.</t>
+          <t>smittväg, hygien, modell</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>smittväg, hygien, modell</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Infektioner; Undersökningar</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>Infektioner; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M104" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -6922,33 +6581,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G105" s="4" t="inlineStr"/>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>Virus</t>
+        </is>
+      </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>Virus</t>
+          <t>Byggnad och förökning i värdceller.</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>Byggnad och förökning i värdceller.</t>
+          <t>virus, värdcell, förökning</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>virus, värdcell, förökning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t>Infektioner</t>
-        </is>
-      </c>
-      <c r="M105" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -6983,35 +6641,30 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>7.2.1</t>
+          <t>Vita blodkroppar och antikroppar</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>Vita blodkroppar och antikroppar</t>
+          <t>Hur kroppen känner igen och oskadliggör.</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>Hur kroppen känner igen och oskadliggör.</t>
+          <t>vit blodkropp, antikropp, antigen</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>vit blodkropp, antikropp, antigen</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>Infektioner</t>
-        </is>
-      </c>
-      <c r="M106" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -7046,35 +6699,30 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>7.2.2</t>
+          <t>Vaccination</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>Vaccination</t>
+          <t>Hur vaccin fungerar och flockimmunitet.</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>Hur vaccin fungerar och flockimmunitet.</t>
+          <t>vaccin, flockimmunitet</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>vaccin, flockimmunitet</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>Infektioner</t>
-        </is>
-      </c>
-      <c r="M107" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -7109,35 +6757,30 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>7.2.3</t>
+          <t>Antibiotika och resistens</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>Antibiotika och resistens</t>
+          <t>Antibiotika verkar på bakterier, inte virus; resistens uppstår genom naturligt urval; varför antibiotika ska användas rätt.</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>Antibiotika verkar på bakterier, inte virus; resistens uppstår genom naturligt urval; varför antibiotika ska användas rätt.</t>
+          <t>antibiotika, resistens, naturligt urval, mutation</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>antibiotika, resistens, naturligt urval, mutation</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Infektioner; Evolution och mångfald</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>Infektioner; Evolution och mångfald</t>
-        </is>
-      </c>
-      <c r="M108" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -7172,35 +6815,30 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>7.2.L</t>
+          <t>Granska ett vaccinpåstående</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>Granska ett vaccinpåstående</t>
+          <t>Går ett påstående om vaccin att belägga? Sök två källor, bedöm trovärdighet och relevans, sammanfatta.</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>Går ett påstående om vaccin att belägga? Sök två källor, bedöm trovärdighet och relevans, sammanfatta.</t>
+          <t>vaccin, källa, belägg</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>vaccin, källa, belägg</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
+          <t>Infektioner; Informationsgranskning</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>Infektioner; Informationsgranskning</t>
-        </is>
-      </c>
-      <c r="M109" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -7233,33 +6871,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G110" s="4" t="inlineStr"/>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>Barriärer och första försvar</t>
+        </is>
+      </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>Barriärer och första försvar</t>
+          <t>Hud, slemhinnor, inflammation.</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>Hud, slemhinnor, inflammation.</t>
+          <t>hud, slemhinna, inflammation</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>hud, slemhinna, inflammation</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>Infektioner</t>
-        </is>
-      </c>
-      <c r="M110" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -7292,33 +6929,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G111" s="4" t="inlineStr"/>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>Immunologiskt minne</t>
+        </is>
+      </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>Immunologiskt minne</t>
+          <t>Varför man sällan blir sjuk två gånger i samma.</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>Varför man sällan blir sjuk två gånger i samma.</t>
+          <t>immunologiskt minne, immunitet</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>immunologiskt minne, immunitet</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>Infektioner</t>
-        </is>
-      </c>
-      <c r="M111" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -7351,33 +6987,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G112" s="4" t="inlineStr"/>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>Antibiotika</t>
+        </is>
+      </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>Antibiotika</t>
+          <t>Verkar på bakterier, inte virus.</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>Verkar på bakterier, inte virus.</t>
+          <t>antibiotika, bakteriedödande</t>
         </is>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>antibiotika, bakteriedödande</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Infektioner</t>
         </is>
       </c>
       <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>Infektioner</t>
-        </is>
-      </c>
-      <c r="M112" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -7410,33 +7045,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G113" s="4" t="inlineStr"/>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>Granska påståenden om vaccin och smitta</t>
+        </is>
+      </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>Granska påståenden om vaccin och smitta</t>
+          <t>Källkritik och argument.</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>Källkritik och argument.</t>
+          <t>påstående, källa, belägg</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>påstående, källa, belägg</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan; Formulera egna och granska andras argument; kommunicera</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan; Formulera egna och granska andras argument; kommunicera</t>
+          <t>Infektioner; Informationsgranskning; Argumentation</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>Infektioner; Informationsgranskning; Argumentation</t>
-        </is>
-      </c>
-      <c r="M113" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -7471,35 +7105,30 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>8.1.1</t>
+          <t>DNA, gener och kromosomer</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>DNA, gener och kromosomer</t>
+          <t>DNA som arvsmassa; gen, kromosom, genom; hur gener styr egenskaper.</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>DNA som arvsmassa; gen, kromosom, genom; hur gener styr egenskaper.</t>
+          <t>DNA, gen, kromosom, genom, cellkärna, protein, egenskap</t>
         </is>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>DNA, gen, kromosom, genom, cellkärna, protein, egenskap</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Arv och miljö</t>
         </is>
       </c>
       <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>Arv och miljö</t>
-        </is>
-      </c>
-      <c r="M114" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -7534,35 +7163,30 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>8.1.2</t>
+          <t>Anlag och alleler</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>Anlag och alleler</t>
+          <t>Dominant och recessiv; genotyp och fenotyp.</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>Dominant och recessiv; genotyp och fenotyp.</t>
+          <t>allel, dominant, recessiv, genotyp, fenotyp</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>allel, dominant, recessiv, genotyp, fenotyp</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Arv och miljö</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>Arv och miljö</t>
-        </is>
-      </c>
-      <c r="M115" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -7597,35 +7221,30 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>8.1.3</t>
+          <t>Korsningsschema</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>Korsningsschema</t>
+          <t>Sannolikheter vid en egenskap.</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t>Sannolikheter vid en egenskap.</t>
+          <t>korsningsschema, sannolikhet</t>
         </is>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>korsningsschema, sannolikhet</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Arv och miljö</t>
         </is>
       </c>
       <c r="L116" s="4" t="inlineStr">
-        <is>
-          <t>Arv och miljö</t>
-        </is>
-      </c>
-      <c r="M116" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -7660,35 +7279,30 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>8.1.L</t>
+          <t>DNA ur frukt</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>DNA ur frukt</t>
+          <t>Går DNA att göra synligt? Jordgubbe med diskmedel, salt och kall sprit; jämför med och utan diskmedel.</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>Går DNA att göra synligt? Jordgubbe med diskmedel, salt och kall sprit; jämför med och utan diskmedel.</t>
+          <t>DNA, extraktion</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>DNA, extraktion</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Arv och miljö; Undersökningar</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>Arv och miljö; Undersökningar</t>
-        </is>
-      </c>
-      <c r="M117" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -7721,33 +7335,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G118" s="4" t="inlineStr"/>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>DNA</t>
+        </is>
+      </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>DNA</t>
+          <t>Struktur och funktion i stora drag.</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>Struktur och funktion i stora drag.</t>
+          <t>DNA, nukleotid, dubbelhelix</t>
         </is>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>DNA, nukleotid, dubbelhelix</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Arv och miljö</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>Arv och miljö</t>
-        </is>
-      </c>
-      <c r="M118" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -7780,33 +7393,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G119" s="4" t="inlineStr"/>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>Från gen till egenskap</t>
+        </is>
+      </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>Från gen till egenskap</t>
+          <t>Proteiner som mellanled.</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>Proteiner som mellanled.</t>
+          <t>protein, egenskap, genuttryck</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>protein, egenskap, genuttryck</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Arv och miljö</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>Arv och miljö</t>
-        </is>
-      </c>
-      <c r="M119" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -7839,33 +7451,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G120" s="4" t="inlineStr"/>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>Celldelning</t>
+        </is>
+      </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>Celldelning</t>
+          <t>Cellen delar sig; tillväxt och reparation.</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>Cellen delar sig; tillväxt och reparation.</t>
+          <t>mitos, kroppscell, tillväxt</t>
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>mitos, kroppscell, tillväxt</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Arv och miljö; Celler och organsystem</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>Arv och miljö; Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M120" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -7898,33 +7509,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G121" s="4" t="inlineStr"/>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>Könsceller och befruktning</t>
+        </is>
+      </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>Könsceller och befruktning</t>
+          <t>Halverat kromosomtal; ny kombination.</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>Halverat kromosomtal; ny kombination.</t>
+          <t>meios, könscell, befruktning, zygot</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>meios, könscell, befruktning, zygot</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Arv och miljö</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>Arv och miljö</t>
-        </is>
-      </c>
-      <c r="M121" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -7957,33 +7567,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G122" s="4" t="inlineStr"/>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>Ärftliga sjukdomar och stamträd</t>
+        </is>
+      </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>Ärftliga sjukdomar och stamträd</t>
+          <t>Hur en egenskap följer släkten.</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>Hur en egenskap följer släkten.</t>
+          <t>stamträd, ärftlig sjukdom, bärare</t>
         </is>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>stamträd, ärftlig sjukdom, bärare</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Arv och miljö; Hälsa</t>
         </is>
       </c>
       <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>Arv och miljö; Hälsa</t>
-        </is>
-      </c>
-      <c r="M122" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -8018,35 +7627,30 @@
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>8.2.1</t>
+          <t>Arv och miljö</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
+          <t>Egenskaper formas av båda; tvillingar som exempel.</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>arv, miljö, variation, tvillingstudier</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
           <t>Arv och miljö</t>
         </is>
       </c>
-      <c r="I123" s="4" t="inlineStr">
-        <is>
-          <t>Egenskaper formas av båda; tvillingar som exempel.</t>
-        </is>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>arv, miljö, variation, tvillingstudier</t>
-        </is>
-      </c>
-      <c r="K123" s="4" t="inlineStr">
-        <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
-        </is>
-      </c>
       <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>Arv och miljö</t>
-        </is>
-      </c>
-      <c r="M123" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -8081,35 +7685,30 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>8.2.2</t>
+          <t>Gensax, GMO och kloning</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>Gensax, GMO och kloning</t>
+          <t>Principer i enkel form.</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>Principer i enkel form.</t>
+          <t>GMO, gensax (CRISPR), kloning</t>
         </is>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>GMO, gensax (CRISPR), kloning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Genteknik</t>
         </is>
       </c>
       <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>Genteknik</t>
-        </is>
-      </c>
-      <c r="M124" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -8144,35 +7743,30 @@
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>8.2.3</t>
+          <t>Etiska frågor</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>Etiska frågor</t>
+          <t>Vad vi bör göra – inte bara vad vi kan.</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>Vad vi bör göra – inte bara vad vi kan.</t>
+          <t>etik, försiktighetsprincipen, integritet</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>etik, försiktighetsprincipen, integritet</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa; Formulera egna och granska andras argument; kommunicera</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa; Formulera egna och granska andras argument; kommunicera</t>
+          <t>Genteknik; Argumentation</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>Genteknik; Argumentation</t>
-        </is>
-      </c>
-      <c r="M125" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -8207,35 +7801,30 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>8.2.L</t>
+          <t>Etisk bedömning av genteknik</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>Etisk bedömning av genteknik</t>
+          <t>Vilka argument finns för och emot en genteknisk användning? Strukturerad diskussion med roller, belägg och motargument.</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
-          <t>Vilka argument finns för och emot en genteknisk användning? Strukturerad diskussion med roller, belägg och motargument.</t>
+          <t>möjlighet, risk, etik, argument</t>
         </is>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>möjlighet, risk, etik, argument</t>
+          <t>Formulera egna och granska andras argument; kommunicera; Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>Formulera egna och granska andras argument; kommunicera; Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
+          <t>Genteknik; Argumentation</t>
         </is>
       </c>
       <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>Genteknik; Argumentation</t>
-        </is>
-      </c>
-      <c r="M126" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -8268,33 +7857,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G127" s="4" t="inlineStr"/>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>Mutationer</t>
+        </is>
+      </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>Mutationer</t>
+          <t>Vad de är och varför de skapar variation.</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>Vad de är och varför de skapar variation.</t>
+          <t>mutation, variation</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>mutation, variation</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Arv och miljö; Evolution och mångfald</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>Arv och miljö; Evolution och mångfald</t>
-        </is>
-      </c>
-      <c r="M127" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -8327,33 +7915,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G128" s="4" t="inlineStr"/>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>Förädling och genteknik</t>
+        </is>
+      </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>Förädling och genteknik</t>
+          <t>Urval över generationer jämfört med att ändra gener direkt.</t>
         </is>
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>Urval över generationer jämfört med att ändra gener direkt.</t>
+          <t>förädling, urval, genteknik</t>
         </is>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>förädling, urval, genteknik</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Genteknik</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>Genteknik</t>
-        </is>
-      </c>
-      <c r="M128" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -8386,33 +7973,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G129" s="4" t="inlineStr"/>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>Medicin</t>
+        </is>
+      </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>Medicin</t>
+          <t>Insulin, genterapi, vaccin.</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>Insulin, genterapi, vaccin.</t>
+          <t>insulin, genterapi</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>insulin, genterapi</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Genteknik</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>Genteknik</t>
-        </is>
-      </c>
-      <c r="M129" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -8445,33 +8031,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G130" s="4" t="inlineStr"/>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>Jordbruk och livsmedel</t>
+        </is>
+      </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>Jordbruk och livsmedel</t>
+          <t>Förädlade och modifierade grödor.</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>Förädlade och modifierade grödor.</t>
+          <t>modifierad gröda, resistens</t>
         </is>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>modifierad gröda, resistens</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Genteknik</t>
         </is>
       </c>
       <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>Genteknik</t>
-        </is>
-      </c>
-      <c r="M130" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -8504,33 +8089,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G131" s="4" t="inlineStr"/>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>Släktskap och identifiering</t>
+        </is>
+      </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>Släktskap och identifiering</t>
+          <t>DNA-profil, genetiska tester.</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>DNA-profil, genetiska tester.</t>
+          <t>DNA-profil, släktskap, genetiskt test</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>DNA-profil, släktskap, genetiskt test</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Genteknik</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
-        <is>
-          <t>Genteknik</t>
-        </is>
-      </c>
-      <c r="M131" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -8563,33 +8147,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G132" s="4" t="inlineStr"/>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>Möjligheter och risker</t>
+        </is>
+      </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Möjligheter och risker</t>
+          <t>Nytta, osäkerhet, regler.</t>
         </is>
       </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
-          <t>Nytta, osäkerhet, regler.</t>
+          <t>möjlighet, risk, regelverk</t>
         </is>
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
-          <t>möjlighet, risk, regelverk</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
+          <t>Genteknik</t>
         </is>
       </c>
       <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>Genteknik</t>
-        </is>
-      </c>
-      <c r="M132" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -8624,35 +8207,30 @@
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>9.1.1</t>
+          <t>Jordens och livets tidslinje</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>Jordens och livets tidslinje</t>
+          <t>Jordens ålder, de första cellerna, flercelligt liv.</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>Jordens ålder, de första cellerna, flercelligt liv.</t>
+          <t>tidslinje, första celler, flercelligt liv</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>tidslinje, första celler, flercelligt liv</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald</t>
-        </is>
-      </c>
-      <c r="M133" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -8687,35 +8265,30 @@
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>9.1.2</t>
+          <t>Fossil och massutdöenden</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Fossil och massutdöenden</t>
+          <t>Hur fossil bildas och berättar.</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>Hur fossil bildas och berättar.</t>
+          <t>fossil, massutdöende, geologisk tid</t>
         </is>
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>fossil, massutdöende, geologisk tid</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald</t>
-        </is>
-      </c>
-      <c r="M134" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -8750,35 +8323,30 @@
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>9.1.3</t>
+          <t>Fossil och jämförande anatomi</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>Fossil och jämförande anatomi</t>
+          <t>Släktskap som syns i byggnad.</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>Släktskap som syns i byggnad.</t>
+          <t>fossil, homologa organ, släktskap</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>fossil, homologa organ, släktskap</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald; Modeller och historia</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald; Modeller och historia</t>
-        </is>
-      </c>
-      <c r="M135" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -8813,35 +8381,30 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>9.1.L</t>
+          <t>Jämför skelett och bygg släktträd</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>Jämför skelett och bygg släktträd</t>
+          <t>Vad visar likheter i byggnad om släktskap? Jämför ben i framben hos olika däggdjur med digitala bilder; rita ett enkelt släktträd.</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>Vad visar likheter i byggnad om släktskap? Jämför ben i framben hos olika däggdjur med digitala bilder; rita ett enkelt släktträd.</t>
+          <t>homologa organ, släktskap, släktträd</t>
         </is>
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
-          <t>homologa organ, släktskap, släktträd</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Evolution och mångfald; Modeller och historia</t>
         </is>
       </c>
       <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald; Modeller och historia</t>
-        </is>
-      </c>
-      <c r="M136" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -8874,33 +8437,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G137" s="4" t="inlineStr"/>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>Hur kan livet ha uppstått?</t>
+        </is>
+      </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>Hur kan livet ha uppstått?</t>
+          <t>Naturvetenskapliga hypoteser och vad som är osäkert.</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>Naturvetenskapliga hypoteser och vad som är osäkert.</t>
+          <t>hypotes, livets uppkomst, osäkerhet</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>hypotes, livets uppkomst, osäkerhet</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald; Modeller och historia</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald; Modeller och historia</t>
-        </is>
-      </c>
-      <c r="M137" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -8933,33 +8495,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G138" s="4" t="inlineStr"/>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>DNA och direkta observationer</t>
+        </is>
+      </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>DNA och direkta observationer</t>
+          <t>Släktskap i gener; evolution som sker nu.</t>
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>Släktskap i gener; evolution som sker nu.</t>
+          <t>DNA-jämförelse, direkt observation</t>
         </is>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
-          <t>DNA-jämförelse, direkt observation</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald; Arv och miljö</t>
         </is>
       </c>
       <c r="L138" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald; Arv och miljö</t>
-        </is>
-      </c>
-      <c r="M138" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -8994,35 +8555,30 @@
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>9.2.1</t>
+          <t>Variation och naturligt urval</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>Variation och naturligt urval</t>
+          <t>Variation och mutationer som grund; överlevnad och fortplantning; anpassning över generationer.</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>Variation och mutationer som grund; överlevnad och fortplantning; anpassning över generationer.</t>
+          <t>variation, mutation, naturligt urval, anpassning, fortplantning</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>variation, mutation, naturligt urval, anpassning, fortplantning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald; Arv och miljö</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald; Arv och miljö</t>
-        </is>
-      </c>
-      <c r="M139" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -9057,35 +8613,30 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>9.2.2</t>
+          <t>Artbildning</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>Artbildning</t>
+          <t>Isolering och särutveckling.</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>Isolering och särutveckling.</t>
+          <t>art, isolering, artbildning</t>
         </is>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>art, isolering, artbildning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald</t>
-        </is>
-      </c>
-      <c r="M140" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -9120,31 +8671,26 @@
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>9.2.3</t>
+          <t>Naturvetenskap och andra sätt att förklara</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>Naturvetenskap och andra sätt att förklara</t>
+          <t>Vad vetenskap kan och inte kan pröva.</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>Vad vetenskap kan och inte kan pröva.</t>
+          <t>naturvetenskaplig förklaring, prövbarhet</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>naturvetenskaplig förklaring, prövbarhet</t>
-        </is>
-      </c>
-      <c r="K141" s="4" t="inlineStr">
-        <is>
           <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
-      <c r="L141" s="4" t="inlineStr"/>
-      <c r="M141" s="4" t="inlineStr">
+      <c r="K141" s="4" t="inlineStr"/>
+      <c r="L141" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -9179,35 +8725,30 @@
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>9.2.L</t>
+          <t>Modellförsök om urval</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>Modellförsök om urval</t>
+          <t>Hur påverkar kamouflage chansen att bli upptäckt? Färgade bytespunkter på olika bakgrund; mät andel som hittas.</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
-          <t>Hur påverkar kamouflage chansen att bli upptäckt? Färgade bytespunkter på olika bakgrund; mät andel som hittas.</t>
+          <t>naturligt urval, kamouflage, modell</t>
         </is>
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>naturligt urval, kamouflage, modell</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Evolution och mångfald; Undersökningar; Modeller och historia</t>
         </is>
       </c>
       <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald; Undersökningar; Modeller och historia</t>
-        </is>
-      </c>
-      <c r="M142" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -9240,33 +8781,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G143" s="4" t="inlineStr"/>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>Variation och mutationer</t>
+        </is>
+      </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>Variation och mutationer</t>
+          <t>Källor till skillnader.</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>Källor till skillnader.</t>
+          <t>variation, mutation, ärftlighet</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>variation, mutation, ärftlighet</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald; Arv och miljö</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald; Arv och miljö</t>
-        </is>
-      </c>
-      <c r="M143" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -9299,33 +8839,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G144" s="4" t="inlineStr"/>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>Människans ursprung</t>
+        </is>
+      </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>Människans ursprung</t>
+          <t>Primater och tidiga människor.</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
-          <t>Primater och tidiga människor.</t>
+          <t>primat, människans utveckling</t>
         </is>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>primat, människans utveckling</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald</t>
         </is>
       </c>
       <c r="L144" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald</t>
-        </is>
-      </c>
-      <c r="M144" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -9358,33 +8897,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G145" s="4" t="inlineStr"/>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>Darwin och förklaringens historia</t>
+        </is>
+      </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>Darwin och förklaringens historia</t>
+          <t>Hur teorin växte fram och prövas.</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>Hur teorin växte fram och prövas.</t>
+          <t>Darwin, teori, förklaringsmodell</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>Darwin, teori, förklaringsmodell</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald; Modeller och historia</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald; Modeller och historia</t>
-        </is>
-      </c>
-      <c r="M145" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -9419,35 +8957,30 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>10.1.1</t>
+          <t>Stress i kroppen</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>Stress i kroppen</t>
+          <t>Reaktion, kort och lång stress.</t>
         </is>
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>Reaktion, kort och lång stress.</t>
+          <t>stress, stresshormon, stressreaktion</t>
         </is>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>stress, stresshormon, stressreaktion</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Hälsa; Celler och organsystem</t>
         </is>
       </c>
       <c r="L146" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa; Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M146" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -9482,35 +9015,30 @@
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>10.1.2</t>
+          <t>Sömn och motion</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>Sömn och motion</t>
+          <t>Vad sömn och fysisk aktivitet gör för kroppen och psyket; råd och effekter.</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>Vad sömn och fysisk aktivitet gör för kroppen och psyket; råd och effekter.</t>
+          <t>sömn, dygnsrytm, kondition, fysisk aktivitet</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>sömn, dygnsrytm, kondition, fysisk aktivitet</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa</t>
-        </is>
-      </c>
-      <c r="M147" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -9545,35 +9073,30 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>10.1.3</t>
+          <t>Psykisk ohälsa och stöd</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>Psykisk ohälsa och stöd</t>
+          <t>Sakligt om ohälsa och var man får hjälp.</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>Sakligt om ohälsa och var man får hjälp.</t>
+          <t>psykisk ohälsa, stöd, hjälp</t>
         </is>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>psykisk ohälsa, stöd, hjälp</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa</t>
-        </is>
-      </c>
-      <c r="M148" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -9608,35 +9131,30 @@
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>10.1.L</t>
+          <t>Sömn och vanor: statistik</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>Sömn och vanor: statistik</t>
+          <t>Vad säger statistik om sömn bland unga? Läs och tolka ett diagram från en myndighet; formulera en slutsats och en fråga.</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>Vad säger statistik om sömn bland unga? Läs och tolka ett diagram från en myndighet; formulera en slutsats och en fråga.</t>
+          <t>statistik, diagram, slutsats</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>statistik, diagram, slutsats</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder; Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder; Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
+          <t>Hälsa; Undersökningar; Informationsgranskning</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa; Undersökningar; Informationsgranskning</t>
-        </is>
-      </c>
-      <c r="M149" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -9669,33 +9187,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G150" s="4" t="inlineStr"/>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>Nervsystemet och sinnena</t>
+        </is>
+      </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>Nervsystemet och sinnena</t>
+          <t>Hjärna, ryggmärg, nerver; reflex.</t>
         </is>
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>Hjärna, ryggmärg, nerver; reflex.</t>
+          <t>nervsystem, hjärna, ryggmärg, reflex, sinne</t>
         </is>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>nervsystem, hjärna, ryggmärg, reflex, sinne</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="L150" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M150" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -9728,33 +9245,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G151" s="4" t="inlineStr"/>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>Hormoner och balans</t>
+        </is>
+      </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>Hormoner och balans</t>
+          <t>Hur hormoner verkar; blodsockerreglering som exempel.</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>Hur hormoner verkar; blodsockerreglering som exempel.</t>
+          <t>hormon, blodsocker, insulin, återkoppling</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>hormon, blodsocker, insulin, återkoppling</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M151" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -9787,29 +9303,28 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G152" s="4" t="inlineStr"/>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>Levnadsförhållanden och hälsa</t>
+        </is>
+      </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>Levnadsförhållanden och hälsa</t>
+          <t>Hur miljö, ekonomi och relationer påverkar.</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>Hur miljö, ekonomi och relationer påverkar.</t>
-        </is>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
           <t>levnadsförhållanden, hälsa, skillnader i hälsa</t>
         </is>
       </c>
-      <c r="K152" s="4" t="inlineStr"/>
+      <c r="J152" s="4" t="inlineStr"/>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>Hälsa</t>
+        </is>
+      </c>
       <c r="L152" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa</t>
-        </is>
-      </c>
-      <c r="M152" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -9842,33 +9357,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G153" s="4" t="inlineStr"/>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>Fysisk aktivitet</t>
+        </is>
+      </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>Fysisk aktivitet</t>
+          <t>Effekter på kroppen.</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>Effekter på kroppen.</t>
+          <t>kondition, styrka, fysisk aktivitet</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>kondition, styrka, fysisk aktivitet</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="L153" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa</t>
-        </is>
-      </c>
-      <c r="M153" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -9901,33 +9415,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G154" s="4" t="inlineStr"/>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>Levnadsvanor och sjukdom</t>
+        </is>
+      </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>Levnadsvanor och sjukdom</t>
+          <t>Hjärt-kärlsjukdom och typ 2-diabetes som exempel.</t>
         </is>
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>Hjärt-kärlsjukdom och typ 2-diabetes som exempel.</t>
+          <t>folksjukdom, hjärt-kärlsjukdom, typ 2-diabetes</t>
         </is>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>folksjukdom, hjärt-kärlsjukdom, typ 2-diabetes</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa</t>
-        </is>
-      </c>
-      <c r="M154" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -9962,35 +9475,30 @@
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>10.2.1</t>
+          <t>Alkohol, tobak, nikotin och droger</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>Alkohol, tobak, nikotin och droger</t>
+          <t>Effekter och risker; narkotika och lagstiftning.</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>Effekter och risker; narkotika och lagstiftning.</t>
+          <t>alkohol, tobak, nikotin, cannabis, narkotika, lagstiftning</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>alkohol, tobak, nikotin, cannabis, narkotika, lagstiftning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa</t>
-        </is>
-      </c>
-      <c r="M155" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -10025,35 +9533,30 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>10.2.2</t>
+          <t>Hjärnan och beroende</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>Hjärnan och beroende</t>
+          <t>Belöningssystemet.</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>Belöningssystemet.</t>
+          <t>belöningssystem, beroende, tolerans, abstinens</t>
         </is>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>belöningssystem, beroende, tolerans, abstinens</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Hälsa; Celler och organsystem</t>
         </is>
       </c>
       <c r="L156" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa; Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M156" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -10088,35 +9591,30 @@
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>10.2.3</t>
+          <t>Förebyggande och stöd</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>Förebyggande och stöd</t>
+          <t>Individ och samhälle.</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>Individ och samhälle.</t>
+          <t>förebyggande, stöd, samhällsinsats</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>förebyggande, stöd, samhällsinsats</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa; Formulera egna och granska andras argument; kommunicera</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa; Formulera egna och granska andras argument; kommunicera</t>
+          <t>Hälsa; Argumentation</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa; Argumentation</t>
-        </is>
-      </c>
-      <c r="M157" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -10151,35 +9649,30 @@
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>10.2.L</t>
+          <t>Läs och tolka statistik om tobak och alkohol</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>Läs och tolka statistik om tobak och alkohol</t>
+          <t>Vad visar statistiken om användning bland unga? Tolka ett diagram från en myndighet; ange vad diagrammet visar och inte visar.</t>
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>Vad visar statistiken om användning bland unga? Tolka ett diagram från en myndighet; ange vad diagrammet visar och inte visar.</t>
+          <t>statistik, diagram, urval</t>
         </is>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>statistik, diagram, urval</t>
+          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder; Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>Färdigheter i att hantera material, utrustning och digitala verktyg; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder; Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
+          <t>Hälsa; Undersökningar; Informationsgranskning</t>
         </is>
       </c>
       <c r="L158" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa; Undersökningar; Informationsgranskning</t>
-        </is>
-      </c>
-      <c r="M158" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -10212,33 +9705,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G159" s="4" t="inlineStr"/>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>Cannabis och andra droger</t>
+        </is>
+      </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>Cannabis och andra droger</t>
+          <t>Effekter, risker och lagar.</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>Effekter, risker och lagar.</t>
+          <t>cannabis, narkotika, lagstiftning</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>cannabis, narkotika, lagstiftning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Hälsa</t>
         </is>
       </c>
       <c r="L159" s="4" t="inlineStr">
-        <is>
-          <t>Hälsa</t>
-        </is>
-      </c>
-      <c r="M159" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -10273,35 +9765,30 @@
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>11.1.1</t>
+          <t>Pubertet och könsorgan</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>Pubertet och könsorgan</t>
+          <t>Hormoner och kroppens förändringar; könsorganens byggnad och funktion; menstruation och sädesutlösning.</t>
         </is>
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>Hormoner och kroppens förändringar; könsorganens byggnad och funktion; menstruation och sädesutlösning.</t>
+          <t>pubertet, könshormon, äggstock, testikel, livmoder, menstruation, sädesutlösning</t>
         </is>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>pubertet, könshormon, äggstock, testikel, livmoder, menstruation, sädesutlösning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Reproduktion och relationer; Celler och organsystem</t>
         </is>
       </c>
       <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>Reproduktion och relationer; Celler och organsystem</t>
-        </is>
-      </c>
-      <c r="M160" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -10336,35 +9823,30 @@
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>11.1.2</t>
+          <t>Befruktning och graviditet</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>Befruktning och graviditet</t>
+          <t>Från könsceller till foster; graviditetens skeden och hälsa; förlossningen i stora drag.</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>Från könsceller till foster; graviditetens skeden och hälsa; förlossningen i stora drag.</t>
+          <t>äggcell, spermie, befruktning, embryo, foster, moderkaka, förlossning</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>äggcell, spermie, befruktning, embryo, foster, moderkaka, förlossning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="L161" s="4" t="inlineStr">
-        <is>
-          <t>Reproduktion och relationer</t>
-        </is>
-      </c>
-      <c r="M161" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -10399,35 +9881,30 @@
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>11.1.3</t>
+          <t>Preventivmedel och STI</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>Preventivmedel och STI</t>
+          <t>Preventivmedel och skydd, nödpreventivmedel; vanliga STI, skydd, test och behandling.</t>
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>Preventivmedel och skydd, nödpreventivmedel; vanliga STI, skydd, test och behandling.</t>
+          <t>preventivmedel, kondom, nödpreventivmedel, STI, klamydia, HIV, HPV, provtagning</t>
         </is>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>preventivmedel, kondom, nödpreventivmedel, STI, klamydia, HIV, HPV, provtagning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Reproduktion och relationer; Infektioner</t>
         </is>
       </c>
       <c r="L162" s="4" t="inlineStr">
-        <is>
-          <t>Reproduktion och relationer; Infektioner</t>
-        </is>
-      </c>
-      <c r="M162" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -10462,35 +9939,30 @@
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>11.1.L</t>
+          <t>Faktagranska information om skydd</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>Faktagranska information om skydd</t>
+          <t>Hur kan man bedöma information om preventivmedel och STI? Granska två kvalitetssäkrade källor och en vilseledande; jämför.</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>Hur kan man bedöma information om preventivmedel och STI? Granska två kvalitetssäkrade källor och en vilseledande; jämför.</t>
+          <t>källa, relevans, trovärdighet</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>källa, relevans, trovärdighet</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
+          <t>Reproduktion och relationer; Informationsgranskning</t>
         </is>
       </c>
       <c r="L163" s="4" t="inlineStr">
-        <is>
-          <t>Reproduktion och relationer; Informationsgranskning</t>
-        </is>
-      </c>
-      <c r="M163" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -10523,33 +9995,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G164" s="4" t="inlineStr"/>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>Könsorgan och menscykel</t>
+        </is>
+      </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>Könsorgan och menscykel</t>
+          <t>Byggnad och funktion.</t>
         </is>
       </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
-          <t>Byggnad och funktion.</t>
+          <t>äggstock, testikel, livmoder, menstruation, sädesutlösning</t>
         </is>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>äggstock, testikel, livmoder, menstruation, sädesutlösning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="L164" s="4" t="inlineStr">
-        <is>
-          <t>Reproduktion och relationer</t>
-        </is>
-      </c>
-      <c r="M164" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -10582,33 +10053,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G165" s="4" t="inlineStr"/>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>Graviditet och fosterutveckling</t>
+        </is>
+      </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>Graviditet och fosterutveckling</t>
+          <t>Skeden och hälsa under graviditet.</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>Skeden och hälsa under graviditet.</t>
+          <t>embryo, foster, moderkaka, navelsträng</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>embryo, foster, moderkaka, navelsträng</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="L165" s="4" t="inlineStr">
-        <is>
-          <t>Reproduktion och relationer</t>
-        </is>
-      </c>
-      <c r="M165" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -10641,33 +10111,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G166" s="4" t="inlineStr"/>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>Förlossning</t>
+        </is>
+      </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>Förlossning</t>
+          <t>Förloppet i stora drag.</t>
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
-          <t>Förloppet i stora drag.</t>
+          <t>förlossning, värkar</t>
         </is>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>förlossning, värkar</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="L166" s="4" t="inlineStr">
-        <is>
-          <t>Reproduktion och relationer</t>
-        </is>
-      </c>
-      <c r="M166" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -10700,33 +10169,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G167" s="4" t="inlineStr"/>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>STI</t>
+        </is>
+      </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>Vanliga STI, skydd, test och behandling.</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>Vanliga STI, skydd, test och behandling.</t>
+          <t>STI, klamydia, HIV, HPV, provtagning</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>STI, klamydia, HIV, HPV, provtagning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Reproduktion och relationer; Infektioner</t>
         </is>
       </c>
       <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>Reproduktion och relationer; Infektioner</t>
-        </is>
-      </c>
-      <c r="M167" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -10759,33 +10227,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G168" s="4" t="inlineStr"/>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>Aborträtt och hjälp</t>
+        </is>
+      </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>Aborträtt och hjälp</t>
+          <t>Faktabaserat om lagen och var man får hjälp.</t>
         </is>
       </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
-          <t>Faktabaserat om lagen och var man får hjälp.</t>
+          <t>abort, lagstiftning, rådgivning</t>
         </is>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>abort, lagstiftning, rådgivning</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="L168" s="4" t="inlineStr">
-        <is>
-          <t>Reproduktion och relationer</t>
-        </is>
-      </c>
-      <c r="M168" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -10820,35 +10287,30 @@
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
-          <t>11.2.1</t>
+          <t>Sexualitet och identitet</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>Sexualitet och identitet</t>
+          <t>Sakligt om variation.</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>Sakligt om variation.</t>
+          <t>sexualitet, sexuell läggning, könsidentitet</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>sexualitet, sexuell läggning, könsidentitet</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
-        <is>
-          <t>Reproduktion och relationer</t>
-        </is>
-      </c>
-      <c r="M169" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -10883,35 +10345,30 @@
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>11.2.2</t>
+          <t>Relationer, kärlek och ansvar</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>Relationer, kärlek och ansvar</t>
+          <t>Vad som kännetecknar en god relation.</t>
         </is>
       </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
-          <t>Vad som kännetecknar en god relation.</t>
+          <t>relation, kärlek, ansvar, ömsesidighet</t>
         </is>
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
-          <t>relation, kärlek, ansvar, ömsesidighet</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="L170" s="4" t="inlineStr">
-        <is>
-          <t>Reproduktion och relationer</t>
-        </is>
-      </c>
-      <c r="M170" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -10946,35 +10403,30 @@
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>11.2.3</t>
+          <t>Samtycke och gränser</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>Samtycke och gränser</t>
+          <t>Ömsesidighet, gränser, nätet, våld och var man får hjälp.</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>Ömsesidighet, gränser, nätet, våld och var man får hjälp.</t>
+          <t>samtycke, gräns, övergrepp, stöd</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>samtycke, gräns, övergrepp, stöd</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
+          <t>Reproduktion och relationer</t>
         </is>
       </c>
       <c r="L171" s="4" t="inlineStr">
-        <is>
-          <t>Reproduktion och relationer</t>
-        </is>
-      </c>
-      <c r="M171" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -11009,35 +10461,30 @@
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>11.2.L</t>
+          <t>Samtycke – fallövning</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>Samtycke – fallövning</t>
+          <t>Hur bedömer vi samtycke i olika situationer? Diskutera färdiga fall i grupp: vad är samtycke, gränser, var får man hjälp.</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>Hur bedömer vi samtycke i olika situationer? Diskutera färdiga fall i grupp: vad är samtycke, gränser, var får man hjälp.</t>
+          <t>samtycke, gräns, ömsesidighet</t>
         </is>
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
-          <t>samtycke, gräns, ömsesidighet</t>
+          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa; Formulera egna och granska andras argument; kommunicera</t>
         </is>
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa; Formulera egna och granska andras argument; kommunicera</t>
+          <t>Reproduktion och relationer; Argumentation</t>
         </is>
       </c>
       <c r="L172" s="4" t="inlineStr">
-        <is>
-          <t>Reproduktion och relationer; Argumentation</t>
-        </is>
-      </c>
-      <c r="M172" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -11070,33 +10517,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G173" s="4" t="inlineStr"/>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>Granska information om sex och relationer</t>
+        </is>
+      </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>Granska information om sex och relationer</t>
+          <t>Källkritik och mediebilder.</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>Källkritik och mediebilder.</t>
+          <t>källa, mediebild, påstående</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>källa, mediebild, påstående</t>
+          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>Söka svar med olika typer av källor; kritiskt tänkande och tilltro till den egna förmågan</t>
+          <t>Reproduktion och relationer; Informationsgranskning</t>
         </is>
       </c>
       <c r="L173" s="4" t="inlineStr">
-        <is>
-          <t>Reproduktion och relationer; Informationsgranskning</t>
-        </is>
-      </c>
-      <c r="M173" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -11131,35 +10577,30 @@
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>12.1.1</t>
+          <t>Röda trådar</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>Röda trådar</t>
+          <t>Energi, kretslopp, evolution, samverkan.</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>Energi, kretslopp, evolution, samverkan.</t>
+          <t>energi, kretslopp, evolution, samverkan</t>
         </is>
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
-          <t>energi, kretslopp, evolution, samverkan</t>
+          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>Naturvetenskapens världsbild med evolutionsteorin som grund; skilja naturvetenskapliga från andra sätt att förklara omvärlden; Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Evolution och mångfald; Fotosyntes, kretslopp, energi</t>
         </is>
       </c>
       <c r="L174" s="4" t="inlineStr">
-        <is>
-          <t>Evolution och mångfald; Fotosyntes, kretslopp, energi</t>
-        </is>
-      </c>
-      <c r="M174" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -11194,35 +10635,30 @@
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>12.1.2</t>
+          <t>Planera och värdera en undersökning</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>Planera och värdera en undersökning</t>
+          <t>Träna på hela kedjan.</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>Träna på hela kedjan.</t>
+          <t>hypotes, variabel, felkälla</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>hypotes, variabel, felkälla</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="L175" s="4" t="inlineStr">
-        <is>
-          <t>Undersökningar</t>
-        </is>
-      </c>
-      <c r="M175" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -11257,35 +10693,30 @@
       </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>12.1.3</t>
+          <t>Argumentera i miljö- och hälsofrågor</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>Argumentera i miljö- och hälsofrågor</t>
+          <t>Övningar.</t>
         </is>
       </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t>Övningar.</t>
+          <t>argument, belägg, motargument</t>
         </is>
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
-          <t>argument, belägg, motargument</t>
+          <t>Formulera egna och granska andras argument; kommunicera; Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
         </is>
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>Formulera egna och granska andras argument; kommunicera; Hantera praktiska och etiska valsituationer i frågor om miljö och hälsa</t>
+          <t>Argumentation</t>
         </is>
       </c>
       <c r="L176" s="4" t="inlineStr">
-        <is>
-          <t>Argumentation</t>
-        </is>
-      </c>
-      <c r="M176" s="4" t="inlineStr">
         <is>
           <t>Granska/ta ställning</t>
         </is>
@@ -11320,35 +10751,30 @@
       </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
-          <t>12.1.L</t>
+          <t>Provlik mini-undersökning</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>Provlik mini-undersökning</t>
+          <t>Kan du planera och värdera en undersökning på egen hand? En färdig frågeställning: planera, genomför enkelt, värdera.</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>Kan du planera och värdera en undersökning på egen hand? En färdig frågeställning: planera, genomför enkelt, värdera.</t>
+          <t>variabel, felkälla, slutsats</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>variabel, felkälla, slutsats</t>
+          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
+          <t>Undersökningar</t>
         </is>
       </c>
       <c r="L177" s="4" t="inlineStr">
-        <is>
-          <t>Undersökningar</t>
-        </is>
-      </c>
-      <c r="M177" s="4" t="inlineStr">
         <is>
           <t>Undersöka</t>
         </is>
@@ -11381,33 +10807,32 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G178" s="4" t="inlineStr"/>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>Kroppen som helhet</t>
+        </is>
+      </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>Kroppen som helhet</t>
+          <t>System som samverkar.</t>
         </is>
       </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t>System som samverkar.</t>
+          <t>organsystem, infektion, hälsa</t>
         </is>
       </c>
       <c r="J178" s="4" t="inlineStr">
         <is>
-          <t>organsystem, infektion, hälsa</t>
+          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
         </is>
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband</t>
+          <t>Celler och organsystem; Infektioner; Hälsa</t>
         </is>
       </c>
       <c r="L178" s="4" t="inlineStr">
-        <is>
-          <t>Celler och organsystem; Infektioner; Hälsa</t>
-        </is>
-      </c>
-      <c r="M178" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller</t>
         </is>
@@ -11440,36 +10865,35 @@
           <t>Om tid / fördjupning</t>
         </is>
       </c>
-      <c r="G179" s="4" t="inlineStr"/>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>Provlik uppgiftsserie</t>
+        </is>
+      </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>Provlik uppgiftsserie</t>
+          <t>Blandade uppgifter.</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>Blandade uppgifter.</t>
+          <t>alla begrepp i boken</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t>alla begrepp i boken</t>
-        </is>
-      </c>
-      <c r="K179" s="4" t="inlineStr">
-        <is>
           <t>Kunskaper om natur och människokropp; använda begrepp och förklaringsmodeller för att beskriva och förklara samband; Egna systematiska undersökningar; påståenden kan prövas; kunskap växer fram med naturvetenskapliga arbetsmetoder</t>
         </is>
       </c>
-      <c r="L179" s="4" t="inlineStr"/>
-      <c r="M179" s="4" t="inlineStr">
+      <c r="K179" s="4" t="inlineStr"/>
+      <c r="L179" s="4" t="inlineStr">
         <is>
           <t>Begrepp/modeller; Granska/ta ställning; Undersöka</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M179"/>
+  <autoFilter ref="A1:L179"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
